--- a/Data point Supporting files/Germany 2021/Indicators.xlsx
+++ b/Data point Supporting files/Germany 2021/Indicators.xlsx
@@ -5,7 +5,7 @@
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="3"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0"/>
   </bookViews>
   <sheets>
     <sheet name="Indicators by country" sheetId="1" state="visible" r:id="rId2"/>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="496" uniqueCount="320">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="497" uniqueCount="321">
   <si>
     <t xml:space="preserve">Country</t>
   </si>
@@ -40,22 +40,25 @@
     <t xml:space="preserve">GI 2020</t>
   </si>
   <si>
+    <t xml:space="preserve">ETI 2016</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GPI 2020</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Human right abuse scaled</t>
+  </si>
+  <si>
+    <t xml:space="preserve">WDI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Biodiversity</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DCC</t>
+  </si>
+  <si>
     <t xml:space="preserve">KOFGI</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GPI 2020</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Human right abuse scaled</t>
-  </si>
-  <si>
-    <t xml:space="preserve">WDI</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Biodiversity</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DCC</t>
   </si>
   <si>
     <t xml:space="preserve">Afghanistan</t>
@@ -1135,8 +1138,8 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:J210"/>
-  <sheetFormatPr defaultColWidth="11.23828125" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <dimension ref="A1:K210"/>
+  <sheetFormatPr defaultColWidth="11.2421875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="10.67"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="10.44"/>
@@ -1146,7 +1149,9 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="10.67"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="9.44"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="10"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="26" min="9" style="0" width="10.67"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="9" style="0" width="10.67"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="0" width="9.78"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="26" min="12" style="0" width="10.67"/>
   </cols>
   <sheetData>
     <row r="1" s="4" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1180,10 +1185,13 @@
       <c r="J1" s="3" t="s">
         <v>9</v>
       </c>
+      <c r="K1" s="2" t="s">
+        <v>10</v>
+      </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B2" s="5" t="n">
         <v>60.01984</v>
@@ -1212,10 +1220,13 @@
       <c r="J2" s="3" t="n">
         <v>7.5</v>
       </c>
+      <c r="K2" s="7" t="n">
+        <v>4.3156</v>
+      </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B3" s="5" t="n">
         <v>44.43116</v>
@@ -1244,10 +1255,13 @@
       <c r="J3" s="3" t="n">
         <v>3.6</v>
       </c>
+      <c r="K3" s="6" t="n">
+        <v>0.8818</v>
+      </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B4" s="5" t="n">
         <v>50.669688</v>
@@ -1276,10 +1290,13 @@
       <c r="J4" s="3" t="n">
         <v>4.4</v>
       </c>
+      <c r="K4" s="6" t="n">
+        <v>4.2147</v>
+      </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B5" s="5" t="n">
         <v>32.123328</v>
@@ -1308,10 +1325,13 @@
       <c r="J5" s="3" t="n">
         <v>3.1</v>
       </c>
+      <c r="K5" s="6" t="n">
+        <v>2.118</v>
+      </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B6" s="5" t="n">
         <v>25.840339</v>
@@ -1340,10 +1360,13 @@
       <c r="J6" s="3" t="n">
         <v>2</v>
       </c>
+      <c r="K6" s="6" t="n">
+        <v>1.2532</v>
+      </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B7" s="5" t="n">
         <v>52.648459</v>
@@ -1372,10 +1395,13 @@
       <c r="J7" s="3" t="n">
         <v>7.3</v>
       </c>
+      <c r="K7" s="6" t="n">
+        <v>3.8356</v>
+      </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B8" s="5" t="n">
         <v>34.835405</v>
@@ -1404,10 +1430,13 @@
       <c r="J8" s="3" t="n">
         <v>3.7</v>
       </c>
+      <c r="K8" s="6" t="n">
+        <v>1.5415</v>
+      </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B9" s="5" t="n">
         <v>40.358747</v>
@@ -1436,10 +1465,13 @@
       <c r="J9" s="3" t="n">
         <v>4</v>
       </c>
+      <c r="K9" s="6" t="n">
+        <v>1.9122</v>
+      </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B10" s="5" t="n">
         <v>49.613198</v>
@@ -1468,10 +1500,13 @@
       <c r="J10" s="3" t="n">
         <v>3.9</v>
       </c>
+      <c r="K10" s="6" t="n">
+        <v>3.7514</v>
+      </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B11" s="5" t="n">
         <v>43.00132</v>
@@ -1500,10 +1535,13 @@
       <c r="J11" s="3" t="n">
         <v>2.7</v>
       </c>
+      <c r="K11" s="6" t="n">
+        <v>1.982</v>
+      </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B12" s="5" t="n">
         <v>30.842185</v>
@@ -1532,10 +1570,13 @@
       <c r="J12" s="3" t="n">
         <v>3.2</v>
       </c>
+      <c r="K12" s="6" t="n">
+        <v>1.4032</v>
+      </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B13" s="5" t="n">
         <v>22.773683</v>
@@ -1564,10 +1605,13 @@
       <c r="J13" s="3" t="n">
         <v>2.5</v>
       </c>
+      <c r="K13" s="6" t="n">
+        <v>1.3621</v>
+      </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B14" s="5" t="n">
         <v>23.966445</v>
@@ -1596,10 +1640,13 @@
       <c r="J14" s="3" t="n">
         <v>2.8</v>
       </c>
+      <c r="K14" s="6" t="n">
+        <v>0.5596</v>
+      </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B15" s="5" t="n">
         <v>46.768845</v>
@@ -1628,10 +1675,13 @@
       <c r="J15" s="3" t="n">
         <v>4.3</v>
       </c>
+      <c r="K15" s="6" t="n">
+        <v>2.1295</v>
+      </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="1" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B16" s="5" t="n">
         <v>37.333958</v>
@@ -1660,10 +1710,13 @@
       <c r="J16" s="3" t="n">
         <v>3.7</v>
       </c>
+      <c r="K16" s="6" t="n">
+        <v>1.5326</v>
+      </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B17" s="5" t="n">
         <v>52.590012</v>
@@ -1692,10 +1745,13 @@
       <c r="J17" s="3" t="n">
         <v>4.6</v>
       </c>
+      <c r="K17" s="6" t="n">
+        <v>3.9607</v>
+      </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B18" s="5" t="n">
         <v>33.581779</v>
@@ -1724,10 +1780,13 @@
       <c r="J18" s="3" t="n">
         <v>2.6</v>
       </c>
+      <c r="K18" s="6" t="n">
+        <v>3.6355</v>
+      </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="1" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B19" s="5" t="n">
         <v>50.401845</v>
@@ -1756,10 +1815,13 @@
       <c r="J19" s="3" t="n">
         <v>3</v>
       </c>
+      <c r="K19" s="6" t="n">
+        <v>2.5747</v>
+      </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="1" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B20" s="5" t="n">
         <v>26.182675</v>
@@ -1788,10 +1850,13 @@
       <c r="J20" s="3" t="n">
         <v>3.2</v>
       </c>
+      <c r="K20" s="6" t="n">
+        <v>0.7009</v>
+      </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="1" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B21" s="5" t="n">
         <v>47.064522</v>
@@ -1820,10 +1885,13 @@
       <c r="J21" s="3" t="n">
         <v>5.1</v>
       </c>
+      <c r="K21" s="6" t="n">
+        <v>4.0727</v>
+      </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="1" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B22" s="5" t="n">
         <v>45.69236</v>
@@ -1852,10 +1920,13 @@
       <c r="J22" s="3" t="n">
         <v>7.3</v>
       </c>
+      <c r="K22" s="6" t="n">
+        <v>4.7775</v>
+      </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="1" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B23" s="5" t="n">
         <v>30.359842</v>
@@ -1884,10 +1955,13 @@
       <c r="J23" s="3" t="n">
         <v>2.4</v>
       </c>
+      <c r="K23" s="6" t="n">
+        <v>1.5415</v>
+      </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="1" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B24" s="5" t="n">
         <v>34.992008</v>
@@ -1916,10 +1990,13 @@
       <c r="J24" s="3" t="n">
         <v>4.3</v>
       </c>
+      <c r="K24" s="6" t="n">
+        <v>2.0377</v>
+      </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="1" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B25" s="5" t="n">
         <v>67.687782</v>
@@ -1948,10 +2025,13 @@
       <c r="J25" s="3" t="n">
         <v>5.3</v>
       </c>
+      <c r="K25" s="6" t="n">
+        <v>3.7935</v>
+      </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="1" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B26" s="5" t="n">
         <v>48.79173</v>
@@ -1980,10 +2060,13 @@
       <c r="J26" s="3" t="n">
         <v>4.9</v>
       </c>
+      <c r="K26" s="6" t="n">
+        <v>1.3012</v>
+      </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="1" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B27" s="5" t="n">
         <v>25.342249</v>
@@ -2012,10 +2095,13 @@
       <c r="J27" s="3" t="n">
         <v>5.3</v>
       </c>
+      <c r="K27" s="6" t="n">
+        <v>2.7727</v>
+      </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B28" s="5" t="n">
         <v>52.363309</v>
@@ -2044,10 +2130,13 @@
       <c r="J28" s="3" t="n">
         <v>4.8</v>
       </c>
+      <c r="K28" s="6" t="n">
+        <v>2.6583</v>
+      </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="1" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B29" s="5" t="n">
         <v>31.681604</v>
@@ -2076,10 +2165,13 @@
       <c r="J29" s="3" t="n">
         <v>2.6</v>
       </c>
+      <c r="K29" s="6" t="n">
+        <v>2.2579</v>
+      </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="1" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B30" s="5" t="n">
         <v>42.275963</v>
@@ -2108,10 +2200,13 @@
       <c r="J30" s="3" t="n">
         <v>3.1</v>
       </c>
+      <c r="K30" s="6" t="n">
+        <v>0.7795</v>
+      </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="1" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B31" s="5" t="n">
         <v>43.075419</v>
@@ -2140,10 +2235,13 @@
       <c r="J31" s="3" t="n">
         <v>7.2</v>
       </c>
+      <c r="K31" s="6" t="n">
+        <v>4.0241</v>
+      </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="1" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B32" s="5" t="n">
         <v>56.44061</v>
@@ -2172,10 +2270,13 @@
       <c r="J32" s="3" t="n">
         <v>6.2</v>
       </c>
+      <c r="K32" s="6" t="n">
+        <v>4.558</v>
+      </c>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="1" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B33" s="5" t="n">
         <v>52.789244</v>
@@ -2204,10 +2305,13 @@
       <c r="J33" s="3" t="n">
         <v>5.7</v>
       </c>
+      <c r="K33" s="6" t="n">
+        <v>3.244</v>
+      </c>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="1" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B34" s="5" t="n">
         <v>53.859639</v>
@@ -2236,10 +2340,13 @@
       <c r="J34" s="3" t="n">
         <v>6.8</v>
       </c>
+      <c r="K34" s="6" t="n">
+        <v>4.0049</v>
+      </c>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="1" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B35" s="5" t="n">
         <v>22.104284</v>
@@ -2268,10 +2375,13 @@
       <c r="J35" s="3" t="n">
         <v>2.5</v>
       </c>
+      <c r="K35" s="6" t="n">
+        <v>0.9212</v>
+      </c>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="1" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B36" s="5" t="n">
         <v>37.382649</v>
@@ -2300,10 +2410,13 @@
       <c r="J36" s="3" t="n">
         <v>4.2</v>
       </c>
+      <c r="K36" s="6" t="n">
+        <v>3.8223</v>
+      </c>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="1" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B37" s="5" t="n">
         <v>31.786068</v>
@@ -2332,10 +2445,13 @@
       <c r="J37" s="3" t="n">
         <v>3.3</v>
       </c>
+      <c r="K37" s="6" t="n">
+        <v>1.2887</v>
+      </c>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="1" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B38" s="5" t="n">
         <v>59.371895</v>
@@ -2364,10 +2480,13 @@
       <c r="J38" s="3" t="n">
         <v>8.9</v>
       </c>
+      <c r="K38" s="6" t="n">
+        <v>5.0862</v>
+      </c>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="1" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B39" s="5" t="n">
         <v>57.42125</v>
@@ -2396,10 +2515,13 @@
       <c r="J39" s="3" t="n">
         <v>8.7</v>
       </c>
+      <c r="K39" s="6" t="n">
+        <v>5.2582</v>
+      </c>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="1" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B40" s="5" t="n">
         <v>31.137437</v>
@@ -2428,10 +2550,13 @@
       <c r="J40" s="3" t="n">
         <v>2.4</v>
       </c>
+      <c r="K40" s="6" t="n">
+        <v>1.4791</v>
+      </c>
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="1" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B41" s="5" t="n">
         <v>55.55</v>
@@ -2460,10 +2585,13 @@
       <c r="J41" s="3" t="n">
         <v>3.3</v>
       </c>
+      <c r="K41" s="6" t="n">
+        <v>2.4929</v>
+      </c>
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="1" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B42" s="5" t="n">
         <v>37.433371</v>
@@ -2492,10 +2620,13 @@
       <c r="J42" s="3" t="n">
         <v>3.2</v>
       </c>
+      <c r="K42" s="6" t="n">
+        <v>2.9768</v>
+      </c>
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="1" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B43" s="5" t="n">
         <v>58.087248</v>
@@ -2524,10 +2655,13 @@
       <c r="J43" s="3" t="n">
         <v>7.2</v>
       </c>
+      <c r="K43" s="6" t="n">
+        <v>3.4678</v>
+      </c>
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="1" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B44" s="5" t="n">
         <v>36.492107</v>
@@ -2556,10 +2690,13 @@
       <c r="J44" s="3" t="n">
         <v>2.3</v>
       </c>
+      <c r="K44" s="6" t="n">
+        <v>1.941</v>
+      </c>
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="1" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="B45" s="5" t="n">
         <v>37.764497</v>
@@ -2588,10 +2725,13 @@
       <c r="J45" s="3" t="n">
         <v>3</v>
       </c>
+      <c r="K45" s="6" t="n">
+        <v>0.5588</v>
+      </c>
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="1" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="B46" s="5" t="n">
         <v>48.628673</v>
@@ -2620,10 +2760,13 @@
       <c r="J46" s="3" t="n">
         <v>3.8</v>
       </c>
+      <c r="K46" s="6" t="n">
+        <v>4.0273</v>
+      </c>
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A47" s="1" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="B47" s="5" t="n">
         <v>33.768286</v>
@@ -2652,10 +2795,13 @@
       <c r="J47" s="3" t="n">
         <v>2.7</v>
       </c>
+      <c r="K47" s="6" t="n">
+        <v>0.64</v>
+      </c>
     </row>
     <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A48" s="1" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="B48" s="5" t="n">
         <v>30.080992</v>
@@ -2684,10 +2830,13 @@
       <c r="J48" s="3" t="n">
         <v>1.9</v>
       </c>
+      <c r="K48" s="6" t="n">
+        <v>0.6384</v>
+      </c>
     </row>
     <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A49" s="1" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="B49" s="5" t="n">
         <v>70.82109</v>
@@ -2716,10 +2865,13 @@
       <c r="J49" s="3" t="n">
         <v>8.3</v>
       </c>
+      <c r="K49" s="6" t="n">
+        <v>4.2399</v>
+      </c>
     </row>
     <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A50" s="1" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="B50" s="5" t="n">
         <v>17.700636</v>
@@ -2748,10 +2900,13 @@
       <c r="J50" s="3" t="n">
         <v>0.9</v>
       </c>
+      <c r="K50" s="6" t="n">
+        <v>0.6755</v>
+      </c>
     </row>
     <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A51" s="1" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="B51" s="5" t="n">
         <v>52.163196</v>
@@ -2780,10 +2935,13 @@
       <c r="J51" s="3" t="n">
         <v>6.5</v>
       </c>
+      <c r="K51" s="6" t="n">
+        <v>5.2016</v>
+      </c>
     </row>
     <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A52" s="1" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="B52" s="5" t="n">
         <v>40.365671</v>
@@ -2812,10 +2970,13 @@
       <c r="J52" s="3" t="n">
         <v>3.8</v>
       </c>
+      <c r="K52" s="6" t="n">
+        <v>2.4175</v>
+      </c>
     </row>
     <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A53" s="1" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="B53" s="5" t="n">
         <v>45.39998</v>
@@ -2844,10 +3005,13 @@
       <c r="J53" s="3" t="n">
         <v>4.6</v>
       </c>
+      <c r="K53" s="6" t="n">
+        <v>2.7345</v>
+      </c>
     </row>
     <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A54" s="1" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="B54" s="5" t="n">
         <v>33.93754</v>
@@ -2876,10 +3040,13 @@
       <c r="J54" s="3" t="n">
         <v>5</v>
       </c>
+      <c r="K54" s="6" t="n">
+        <v>3.7973</v>
+      </c>
     </row>
     <row r="55" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A55" s="1" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="B55" s="5" t="n">
         <v>49.386359</v>
@@ -2908,10 +3075,13 @@
       <c r="J55" s="3" t="n">
         <v>4.1</v>
       </c>
+      <c r="K55" s="6" t="n">
+        <v>3.2808</v>
+      </c>
     </row>
     <row r="56" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A56" s="1" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="B56" s="5" t="n">
         <v>48.029956</v>
@@ -2940,10 +3110,13 @@
       <c r="J56" s="3" t="n">
         <v>3.6</v>
       </c>
+      <c r="K56" s="6" t="n">
+        <v>2.4104</v>
+      </c>
     </row>
     <row r="57" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A57" s="1" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="B57" s="5" t="n">
         <v>58.645432</v>
@@ -2972,10 +3145,13 @@
       <c r="J57" s="3" t="n">
         <v>7.1</v>
       </c>
+      <c r="K57" s="6" t="n">
+        <v>4.4215</v>
+      </c>
     </row>
     <row r="58" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A58" s="1" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="B58" s="5" t="n">
         <v>61.024394</v>
@@ -3004,10 +3180,13 @@
       <c r="J58" s="3" t="n">
         <v>7.8</v>
       </c>
+      <c r="K58" s="6" t="n">
+        <v>5.0203</v>
+      </c>
     </row>
     <row r="59" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A59" s="1" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="B59" s="5" t="n">
         <v>25.087012</v>
@@ -3036,10 +3215,13 @@
       <c r="J59" s="3" t="n">
         <v>1.5</v>
       </c>
+      <c r="K59" s="6" t="n">
+        <v>0.5722</v>
+      </c>
     </row>
     <row r="60" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A60" s="1" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="B60" s="5" t="n">
         <v>50.452285</v>
@@ -3068,10 +3250,13 @@
       <c r="J60" s="3" t="n">
         <v>6.9</v>
       </c>
+      <c r="K60" s="6" t="n">
+        <v>4.098</v>
+      </c>
     </row>
     <row r="61" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A61" s="1" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="B61" s="5" t="n">
         <v>38.599652</v>
@@ -3100,10 +3285,13 @@
       <c r="J61" s="3" t="n">
         <v>3.4</v>
       </c>
+      <c r="K61" s="6" t="n">
+        <v>3.0374</v>
+      </c>
     </row>
     <row r="62" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A62" s="1" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="B62" s="5" t="n">
         <v>11.14428</v>
@@ -3132,10 +3320,13 @@
       <c r="J62" s="3" t="n">
         <v>1.7</v>
       </c>
+      <c r="K62" s="6" t="n">
+        <v>0.6274</v>
+      </c>
     </row>
     <row r="63" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A63" s="1" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B63" s="5" t="n">
         <v>26.924222</v>
@@ -3164,10 +3355,13 @@
       <c r="J63" s="3" t="n">
         <v>2</v>
       </c>
+      <c r="K63" s="6" t="n">
+        <v>0.5233</v>
+      </c>
     </row>
     <row r="64" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A64" s="1" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="B64" s="5" t="n">
         <v>28.103307</v>
@@ -3196,10 +3390,13 @@
       <c r="J64" s="3" t="n">
         <v>2.3</v>
       </c>
+      <c r="K64" s="6" t="n">
+        <v>1.1918</v>
+      </c>
     </row>
     <row r="65" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A65" s="1" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="B65" s="5" t="n">
         <v>51.718137</v>
@@ -3228,10 +3425,13 @@
       <c r="J65" s="3" t="n">
         <v>5.9</v>
       </c>
+      <c r="K65" s="6" t="n">
+        <v>5.012</v>
+      </c>
     </row>
     <row r="66" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A66" s="1" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="B66" s="5" t="n">
         <v>48.085848</v>
@@ -3260,10 +3460,13 @@
       <c r="J66" s="3" t="n">
         <v>6.3</v>
       </c>
+      <c r="K66" s="6" t="n">
+        <v>4.7113</v>
+      </c>
     </row>
     <row r="67" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A67" s="1" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="B67" s="5" t="n">
         <v>35.884488</v>
@@ -3292,10 +3495,13 @@
       <c r="J67" s="3" t="n">
         <v>2.4</v>
       </c>
+      <c r="K67" s="6" t="n">
+        <v>1.0466</v>
+      </c>
     </row>
     <row r="68" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A68" s="1" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B68" s="5" t="n">
         <v>22.34549</v>
@@ -3324,10 +3530,13 @@
       <c r="J68" s="3" t="n">
         <v>1.8</v>
       </c>
+      <c r="K68" s="6" t="n">
+        <v>0.5746</v>
+      </c>
     </row>
     <row r="69" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A69" s="1" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="B69" s="5" t="n">
         <v>35.408546</v>
@@ -3356,10 +3565,13 @@
       <c r="J69" s="3" t="n">
         <v>5.1</v>
       </c>
+      <c r="K69" s="6" t="n">
+        <v>3.3358</v>
+      </c>
     </row>
     <row r="70" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A70" s="1" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="B70" s="5" t="n">
         <v>37.159387</v>
@@ -3388,10 +3600,13 @@
       <c r="J70" s="3" t="n">
         <v>3</v>
       </c>
+      <c r="K70" s="6" t="n">
+        <v>0.7456</v>
+      </c>
     </row>
     <row r="71" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A71" s="1" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="B71" s="5" t="n">
         <v>28.906059</v>
@@ -3420,10 +3635,13 @@
       <c r="J71" s="3" t="n">
         <v>3.5</v>
       </c>
+      <c r="K71" s="6" t="n">
+        <v>0.7659</v>
+      </c>
     </row>
     <row r="72" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A72" s="1" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="B72" s="5" t="n">
         <v>40.732294</v>
@@ -3452,10 +3670,13 @@
       <c r="J72" s="3" t="n">
         <v>3.6</v>
       </c>
+      <c r="K72" s="6" t="n">
+        <v>2.6592</v>
+      </c>
     </row>
     <row r="73" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A73" s="1" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="B73" s="5" t="n">
         <v>32.252885</v>
@@ -3484,10 +3705,13 @@
       <c r="J73" s="3" t="n">
         <v>3.1</v>
       </c>
+      <c r="K73" s="6" t="n">
+        <v>2.118</v>
+      </c>
     </row>
     <row r="74" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A74" s="1" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="B74" s="5" t="n">
         <v>52.069602</v>
@@ -3516,10 +3740,13 @@
       <c r="J74" s="3" t="n">
         <v>5</v>
       </c>
+      <c r="K74" s="6" t="n">
+        <v>2.5303</v>
+      </c>
     </row>
     <row r="75" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A75" s="1" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="B75" s="5" t="n">
         <v>37.708258</v>
@@ -3548,10 +3775,13 @@
       <c r="J75" s="3" t="n">
         <v>7.4</v>
       </c>
+      <c r="K75" s="6" t="n">
+        <v>5.0046</v>
+      </c>
     </row>
     <row r="76" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A76" s="1" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="B76" s="5" t="n">
         <v>57.274316</v>
@@ -3580,10 +3810,13 @@
       <c r="J76" s="3" t="n">
         <v>7.7</v>
       </c>
+      <c r="K76" s="6" t="n">
+        <v>4.4268</v>
+      </c>
     </row>
     <row r="77" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A77" s="1" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="B77" s="5" t="n">
         <v>45.891539</v>
@@ -3612,10 +3845,13 @@
       <c r="J77" s="3" t="n">
         <v>5</v>
       </c>
+      <c r="K77" s="6" t="n">
+        <v>4.6483</v>
+      </c>
     </row>
     <row r="78" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A78" s="1" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="B78" s="5" t="n">
         <v>60.879515</v>
@@ -3644,10 +3880,13 @@
       <c r="J78" s="3" t="n">
         <v>7.2</v>
       </c>
+      <c r="K78" s="6" t="n">
+        <v>2.9033</v>
+      </c>
     </row>
     <row r="79" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A79" s="1" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="B79" s="5" t="n">
         <v>52.687493</v>
@@ -3676,10 +3915,13 @@
       <c r="J79" s="3" t="n">
         <v>5.9</v>
       </c>
+      <c r="K79" s="6" t="n">
+        <v>2.8151</v>
+      </c>
     </row>
     <row r="80" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A80" s="1" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B80" s="5" t="n">
         <v>24.85047</v>
@@ -3708,10 +3950,13 @@
       <c r="J80" s="3" t="n">
         <v>1.7</v>
       </c>
+      <c r="K80" s="6" t="n">
+        <v>1.5147</v>
+      </c>
     </row>
     <row r="81" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A81" s="1" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B81" s="5" t="n">
         <v>37.715001</v>
@@ -3740,10 +3985,13 @@
       <c r="J81" s="3" t="n">
         <v>2.7</v>
       </c>
+      <c r="K81" s="6" t="n">
+        <v>0.6117</v>
+      </c>
     </row>
     <row r="82" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A82" s="1" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="B82" s="5" t="n">
         <v>22.061661</v>
@@ -3772,10 +4020,13 @@
       <c r="J82" s="3" t="n">
         <v>2</v>
       </c>
+      <c r="K82" s="6" t="n">
+        <v>0.6555</v>
+      </c>
     </row>
     <row r="83" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A83" s="1" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="B83" s="5" t="n">
         <v>43.610801</v>
@@ -3804,10 +4055,13 @@
       <c r="J83" s="3" t="n">
         <v>4.6</v>
       </c>
+      <c r="K83" s="6" t="n">
+        <v>2.9916</v>
+      </c>
     </row>
     <row r="84" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A84" s="1" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="B84" s="5" t="n">
         <v>55.4</v>
@@ -3836,10 +4090,13 @@
       <c r="J84" s="3" t="n">
         <v>4.1</v>
       </c>
+      <c r="K84" s="6" t="n">
+        <v>2.2937</v>
+      </c>
     </row>
     <row r="85" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A85" s="1" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="B85" s="5" t="n">
         <v>54.750845</v>
@@ -3868,10 +4125,13 @@
       <c r="J85" s="3" t="n">
         <v>5.5</v>
       </c>
+      <c r="K85" s="6" t="n">
+        <v>3.838</v>
+      </c>
     </row>
     <row r="86" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A86" s="1" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="B86" s="5" t="n">
         <v>57.538495</v>
@@ -3900,10 +4160,13 @@
       <c r="J86" s="3" t="n">
         <v>5</v>
       </c>
+      <c r="K86" s="6" t="n">
+        <v>3.4155</v>
+      </c>
     </row>
     <row r="87" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A87" s="1" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="B87" s="5" t="n">
         <v>0</v>
@@ -3932,10 +4195,13 @@
       <c r="J87" s="3" t="n">
         <v>3.1</v>
       </c>
+      <c r="K87" s="6" t="n">
+        <v>1.353</v>
+      </c>
     </row>
     <row r="88" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A88" s="1" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="B88" s="5" t="n">
         <v>29.114712</v>
@@ -3964,10 +4230,13 @@
       <c r="J88" s="3" t="n">
         <v>2.1</v>
       </c>
+      <c r="K88" s="6" t="n">
+        <v>0.8722</v>
+      </c>
     </row>
     <row r="89" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A89" s="1" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="B89" s="5" t="n">
         <v>35.786195</v>
@@ -3996,10 +4265,13 @@
       <c r="J89" s="3" t="n">
         <v>3.5</v>
       </c>
+      <c r="K89" s="6" t="n">
+        <v>0.5556</v>
+      </c>
     </row>
     <row r="90" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A90" s="1" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="B90" s="5" t="n">
         <v>47.898497</v>
@@ -4028,10 +4300,13 @@
       <c r="J90" s="3" t="n">
         <v>6.6</v>
       </c>
+      <c r="K90" s="6" t="n">
+        <v>3.9584</v>
+      </c>
     </row>
     <row r="91" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A91" s="1" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="B91" s="5" t="n">
         <v>41.352221</v>
@@ -4060,10 +4335,13 @@
       <c r="J91" s="3" t="n">
         <v>3.7</v>
       </c>
+      <c r="K91" s="6" t="n">
+        <v>3.4641</v>
+      </c>
     </row>
     <row r="92" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A92" s="1" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="B92" s="5" t="n">
         <v>24.854407</v>
@@ -4092,10 +4370,13 @@
       <c r="J92" s="3" t="n">
         <v>1.1</v>
       </c>
+      <c r="K92" s="6" t="n">
+        <v>1.8686</v>
+      </c>
     </row>
     <row r="93" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A93" s="1" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="B93" s="5" t="n">
         <v>41.311723</v>
@@ -4124,10 +4405,13 @@
       <c r="J93" s="3" t="n">
         <v>3.5</v>
       </c>
+      <c r="K93" s="6" t="n">
+        <v>1.9789</v>
+      </c>
     </row>
     <row r="94" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A94" s="1" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="B94" s="5" t="n">
         <v>40.43</v>
@@ -4156,10 +4440,13 @@
       <c r="J94" s="3" t="n">
         <v>3.4</v>
       </c>
+      <c r="K94" s="6" t="n">
+        <v>2.847</v>
+      </c>
     </row>
     <row r="95" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A95" s="1" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="B95" s="5" t="n">
         <v>48.010865</v>
@@ -4188,10 +4475,13 @@
       <c r="J95" s="3" t="n">
         <v>5.5</v>
       </c>
+      <c r="K95" s="6" t="n">
+        <v>3.5349</v>
+      </c>
     </row>
     <row r="96" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A96" s="1" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="B96" s="5" t="n">
         <v>40.663731</v>
@@ -4220,10 +4510,13 @@
       <c r="J96" s="3" t="n">
         <v>4.5</v>
       </c>
+      <c r="K96" s="6" t="n">
+        <v>3.2689</v>
+      </c>
     </row>
     <row r="97" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A97" s="1" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="B97" s="5" t="n">
         <v>45.451445</v>
@@ -4252,10 +4545,13 @@
       <c r="J97" s="3" t="n">
         <v>5.5</v>
       </c>
+      <c r="K97" s="6" t="n">
+        <v>3.0545</v>
+      </c>
     </row>
     <row r="98" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A98" s="1" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="B98" s="5" t="n">
         <v>41.670081</v>
@@ -4284,10 +4580,13 @@
       <c r="J98" s="3" t="n">
         <v>4</v>
       </c>
+      <c r="K98" s="6" t="n">
+        <v>1.7671</v>
+      </c>
     </row>
     <row r="99" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A99" s="1" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="B99" s="5" t="n">
         <v>52.267973</v>
@@ -4316,10 +4615,13 @@
       <c r="J99" s="3" t="n">
         <v>4.3</v>
       </c>
+      <c r="K99" s="6" t="n">
+        <v>2.5008</v>
+      </c>
     </row>
     <row r="100" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A100" s="1" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="B100" s="5" t="n">
         <v>52.058598</v>
@@ -4348,10 +4650,13 @@
       <c r="J100" s="3" t="n">
         <v>5.8</v>
       </c>
+      <c r="K100" s="6" t="n">
+        <v>2.129</v>
+      </c>
     </row>
     <row r="101" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A101" s="1" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="B101" s="5" t="n">
         <v>31.330395</v>
@@ -4380,10 +4685,13 @@
       <c r="J101" s="3" t="n">
         <v>2.5</v>
       </c>
+      <c r="K101" s="6" t="n">
+        <v>0.6739</v>
+      </c>
     </row>
     <row r="102" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A102" s="1" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="B102" s="5" t="n">
         <v>54.442417</v>
@@ -4412,10 +4720,13 @@
       <c r="J102" s="3" t="n">
         <v>5.5</v>
       </c>
+      <c r="K102" s="6" t="n">
+        <v>2.266</v>
+      </c>
     </row>
     <row r="103" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A103" s="1" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="B103" s="5" t="n">
         <v>47.994331</v>
@@ -4444,10 +4755,13 @@
       <c r="J103" s="3" t="n">
         <v>6.3</v>
       </c>
+      <c r="K103" s="6" t="n">
+        <v>2.3393</v>
+      </c>
     </row>
     <row r="104" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A104" s="1" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="B104" s="5" t="n">
         <v>54.342249</v>
@@ -4476,10 +4790,13 @@
       <c r="J104" s="3" t="n">
         <v>7.3</v>
       </c>
+      <c r="K104" s="6" t="n">
+        <v>5.0946</v>
+      </c>
     </row>
     <row r="105" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A105" s="1" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="B105" s="5" t="n">
         <v>61.228355</v>
@@ -4508,10 +4825,13 @@
       <c r="J105" s="3" t="n">
         <v>6.5</v>
       </c>
+      <c r="K105" s="6" t="n">
+        <v>2.6452</v>
+      </c>
     </row>
     <row r="106" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A106" s="1" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="B106" s="5" t="n">
         <v>23.61109</v>
@@ -4540,10 +4860,13 @@
       <c r="J106" s="3" t="n">
         <v>1.3</v>
       </c>
+      <c r="K106" s="6" t="n">
+        <v>0.6977</v>
+      </c>
     </row>
     <row r="107" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A107" s="1" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="B107" s="5" t="n">
         <v>29.944697</v>
@@ -4572,10 +4895,13 @@
       <c r="J107" s="3" t="n">
         <v>2.5</v>
       </c>
+      <c r="K107" s="6" t="n">
+        <v>0.707</v>
+      </c>
     </row>
     <row r="108" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A108" s="1" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="B108" s="5" t="n">
         <v>20.586048</v>
@@ -4604,10 +4930,13 @@
       <c r="J108" s="3" t="n">
         <v>1.3</v>
       </c>
+      <c r="K108" s="6" t="n">
+        <v>0.4374</v>
+      </c>
     </row>
     <row r="109" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A109" s="1" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="B109" s="5" t="n">
         <v>31.052725</v>
@@ -4636,10 +4965,13 @@
       <c r="J109" s="3" t="n">
         <v>3.3</v>
       </c>
+      <c r="K109" s="6" t="n">
+        <v>0.8552</v>
+      </c>
     </row>
     <row r="110" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A110" s="1" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="B110" s="5" t="n">
         <v>53.033473</v>
@@ -4668,10 +5000,13 @@
       <c r="J110" s="3" t="n">
         <v>7.8</v>
       </c>
+      <c r="K110" s="6" t="n">
+        <v>3.1542</v>
+      </c>
     </row>
     <row r="111" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A111" s="1" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="B111" s="5" t="n">
         <v>48.370466</v>
@@ -4700,10 +5035,13 @@
       <c r="J111" s="3" t="n">
         <v>5.9</v>
       </c>
+      <c r="K111" s="6" t="n">
+        <v>3.1634</v>
+      </c>
     </row>
     <row r="112" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A112" s="1" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="B112" s="5" t="n">
         <v>36.192981</v>
@@ -4732,10 +5070,13 @@
       <c r="J112" s="3" t="n">
         <v>3.9</v>
       </c>
+      <c r="K112" s="6" t="n">
+        <v>1.4609</v>
+      </c>
     </row>
     <row r="113" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A113" s="1" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="B113" s="5" t="n">
         <v>43.600471</v>
@@ -4764,10 +5105,13 @@
       <c r="J113" s="3" t="n">
         <v>3.4</v>
       </c>
+      <c r="K113" s="6" t="n">
+        <v>2.9156</v>
+      </c>
     </row>
     <row r="114" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A114" s="1" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="B114" s="5" t="n">
         <v>50.695978</v>
@@ -4796,10 +5140,13 @@
       <c r="J114" s="3" t="n">
         <v>7.1</v>
       </c>
+      <c r="K114" s="6" t="n">
+        <v>4.0406</v>
+      </c>
     </row>
     <row r="115" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A115" s="1" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="B115" s="5" t="n">
         <v>33.457588</v>
@@ -4828,10 +5175,13 @@
       <c r="J115" s="3" t="n">
         <v>2.5</v>
       </c>
+      <c r="K115" s="6" t="n">
+        <v>0.7731</v>
+      </c>
     </row>
     <row r="116" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A116" s="1" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="B116" s="5" t="n">
         <v>43.422066</v>
@@ -4860,10 +5210,13 @@
       <c r="J116" s="3" t="n">
         <v>3.9</v>
       </c>
+      <c r="K116" s="6" t="n">
+        <v>3.6868</v>
+      </c>
     </row>
     <row r="117" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A117" s="1" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="B117" s="5" t="n">
         <v>33.863709</v>
@@ -4892,10 +5245,13 @@
       <c r="J117" s="3" t="n">
         <v>3.3</v>
       </c>
+      <c r="K117" s="6" t="n">
+        <v>1.8297</v>
+      </c>
     </row>
     <row r="118" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A118" s="1" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="B118" s="5" t="n">
         <v>52.789317</v>
@@ -4924,10 +5280,13 @@
       <c r="J118" s="3" t="n">
         <v>6.6</v>
       </c>
+      <c r="K118" s="6" t="n">
+        <v>4.306</v>
+      </c>
     </row>
     <row r="119" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A119" s="1" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="B119" s="5" t="n">
         <v>34.221399</v>
@@ -4956,10 +5315,13 @@
       <c r="J119" s="3" t="n">
         <v>2.3</v>
       </c>
+      <c r="K119" s="6" t="n">
+        <v>0.6597</v>
+      </c>
     </row>
     <row r="120" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A120" s="1" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="B120" s="5" t="n">
         <v>39.326308</v>
@@ -4988,10 +5350,13 @@
       <c r="J120" s="3" t="n">
         <v>3.4</v>
       </c>
+      <c r="K120" s="6" t="n">
+        <v>1.594</v>
+      </c>
     </row>
     <row r="121" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A121" s="1" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="B121" s="5" t="n">
         <v>40.765091</v>
@@ -5020,10 +5385,13 @@
       <c r="J121" s="3" t="n">
         <v>4.8</v>
       </c>
+      <c r="K121" s="6" t="n">
+        <v>3.5267</v>
+      </c>
     </row>
     <row r="122" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A122" s="1" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="B122" s="5" t="n">
         <v>45.599426</v>
@@ -5052,10 +5420,13 @@
       <c r="J122" s="3" t="n">
         <v>4.3</v>
       </c>
+      <c r="K122" s="6" t="n">
+        <v>1.5566</v>
+      </c>
     </row>
     <row r="123" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A123" s="1" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="B123" s="5" t="n">
         <v>63.351635</v>
@@ -5084,10 +5455,13 @@
       <c r="J123" s="3" t="n">
         <v>3.7</v>
       </c>
+      <c r="K123" s="6" t="n">
+        <v>3.3928</v>
+      </c>
     </row>
     <row r="124" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A124" s="1" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="B124" s="5" t="n">
         <v>41.670607</v>
@@ -5116,10 +5490,13 @@
       <c r="J124" s="3" t="n">
         <v>2.8</v>
       </c>
+      <c r="K124" s="6" t="n">
+        <v>0.8314</v>
+      </c>
     </row>
     <row r="125" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A125" s="1" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="B125" s="5" t="n">
         <v>1.937974</v>
@@ -5148,10 +5525,13 @@
       <c r="J125" s="3" t="n">
         <v>4.1</v>
       </c>
+      <c r="K125" s="6" t="n">
+        <v>2.1599</v>
+      </c>
     </row>
     <row r="126" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A126" s="1" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="B126" s="5" t="n">
         <v>52.567373</v>
@@ -5180,10 +5560,13 @@
       <c r="J126" s="3" t="n">
         <v>7</v>
       </c>
+      <c r="K126" s="6" t="n">
+        <v>2.4247</v>
+      </c>
     </row>
     <row r="127" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A127" s="1" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="B127" s="5" t="n">
         <v>57.473746</v>
@@ -5212,10 +5595,13 @@
       <c r="J127" s="3" t="n">
         <v>6</v>
       </c>
+      <c r="K127" s="6" t="n">
+        <v>2.8977</v>
+      </c>
     </row>
     <row r="128" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A128" s="1" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="B128" s="5" t="n">
         <v>24.763955</v>
@@ -5244,10 +5630,13 @@
       <c r="J128" s="3" t="n">
         <v>4.7</v>
       </c>
+      <c r="K128" s="6" t="n">
+        <v>3.0801</v>
+      </c>
     </row>
     <row r="129" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A129" s="1" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="B129" s="5" t="n">
         <v>41.652573</v>
@@ -5276,10 +5665,13 @@
       <c r="J129" s="3" t="n">
         <v>3.6</v>
       </c>
+      <c r="K129" s="6" t="n">
+        <v>3.0317</v>
+      </c>
     </row>
     <row r="130" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A130" s="1" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="B130" s="5" t="n">
         <v>49.860466</v>
@@ -5308,10 +5700,13 @@
       <c r="J130" s="3" t="n">
         <v>6</v>
       </c>
+      <c r="K130" s="6" t="n">
+        <v>3.6901</v>
+      </c>
     </row>
     <row r="131" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A131" s="1" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="B131" s="5" t="n">
         <v>20.647629</v>
@@ -5340,10 +5735,13 @@
       <c r="J131" s="3" t="n">
         <v>1.8</v>
       </c>
+      <c r="K131" s="6" t="n">
+        <v>0.5052</v>
+      </c>
     </row>
     <row r="132" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A132" s="1" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="B132" s="5" t="n">
         <v>38.811782</v>
@@ -5370,10 +5768,13 @@
         <v>0.656</v>
       </c>
       <c r="J132" s="8"/>
+      <c r="K132" s="6" t="n">
+        <v>0.5233</v>
+      </c>
     </row>
     <row r="133" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A133" s="1" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="B133" s="5" t="n">
         <v>54.29</v>
@@ -5402,10 +5803,13 @@
       <c r="J133" s="3" t="n">
         <v>1.6</v>
       </c>
+      <c r="K133" s="6" t="n">
+        <v>1.6973</v>
+      </c>
     </row>
     <row r="134" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A134" s="1" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="B134" s="5" t="n">
         <v>55.063746</v>
@@ -5434,10 +5838,13 @@
       <c r="J134" s="3" t="n">
         <v>6.2</v>
       </c>
+      <c r="K134" s="6" t="n">
+        <v>2.5004</v>
+      </c>
     </row>
     <row r="135" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A135" s="1" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="B135" s="5" t="n">
         <v>49.662913</v>
@@ -5466,10 +5873,13 @@
       <c r="J135" s="3" t="n">
         <v>7.8</v>
       </c>
+      <c r="K135" s="6" t="n">
+        <v>4.6915</v>
+      </c>
     </row>
     <row r="136" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A136" s="1" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="B136" s="5" t="n">
         <v>54.151706</v>
@@ -5498,10 +5908,13 @@
       <c r="J136" s="3" t="n">
         <v>7.3</v>
       </c>
+      <c r="K136" s="6" t="n">
+        <v>4.9749</v>
+      </c>
     </row>
     <row r="137" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A137" s="1" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="B137" s="5" t="n">
         <v>62.059846</v>
@@ -5530,10 +5943,13 @@
       <c r="J137" s="3" t="n">
         <v>6.5</v>
       </c>
+      <c r="K137" s="6" t="n">
+        <v>4.9682</v>
+      </c>
     </row>
     <row r="138" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A138" s="1" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="B138" s="5" t="n">
         <v>43.444753</v>
@@ -5562,10 +5978,13 @@
       <c r="J138" s="3" t="n">
         <v>4.1</v>
       </c>
+      <c r="K138" s="6" t="n">
+        <v>1.8808</v>
+      </c>
     </row>
     <row r="139" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A139" s="1" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="B139" s="5" t="n">
         <v>28.78</v>
@@ -5594,10 +6013,13 @@
       <c r="J139" s="3" t="n">
         <v>1.5</v>
       </c>
+      <c r="K139" s="6" t="n">
+        <v>0.8065</v>
+      </c>
     </row>
     <row r="140" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A140" s="1" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="B140" s="5" t="n">
         <v>40.145342</v>
@@ -5626,10 +6048,13 @@
       <c r="J140" s="3" t="n">
         <v>3.9</v>
       </c>
+      <c r="K140" s="6" t="n">
+        <v>1.5347</v>
+      </c>
     </row>
     <row r="141" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A141" s="1" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="B141" s="5" t="n">
         <v>50.839022</v>
@@ -5658,10 +6083,13 @@
       <c r="J141" s="3" t="n">
         <v>5.5</v>
       </c>
+      <c r="K141" s="6" t="n">
+        <v>3.5941</v>
+      </c>
     </row>
     <row r="142" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A142" s="1" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="B142" s="5" t="n">
         <v>36.633745</v>
@@ -5690,10 +6118,13 @@
       <c r="J142" s="3" t="n">
         <v>3.2</v>
       </c>
+      <c r="K142" s="6" t="n">
+        <v>2.1135</v>
+      </c>
     </row>
     <row r="143" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A143" s="1" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="B143" s="5" t="n">
         <v>43.371279</v>
@@ -5722,10 +6153,13 @@
       <c r="J143" s="3" t="n">
         <v>5.4</v>
       </c>
+      <c r="K143" s="6" t="n">
+        <v>2.2454</v>
+      </c>
     </row>
     <row r="144" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A144" s="1" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="B144" s="5" t="n">
         <v>54.911622</v>
@@ -5754,10 +6188,13 @@
       <c r="J144" s="3" t="n">
         <v>7.1</v>
       </c>
+      <c r="K144" s="6" t="n">
+        <v>1.8453</v>
+      </c>
     </row>
     <row r="145" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A145" s="1" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="B145" s="5" t="n">
         <v>48.791512</v>
@@ -5786,10 +6223,13 @@
       <c r="J145" s="3" t="n">
         <v>5</v>
       </c>
+      <c r="K145" s="6" t="n">
+        <v>2.675</v>
+      </c>
     </row>
     <row r="146" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A146" s="1" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="B146" s="5" t="n">
         <v>53.715342</v>
@@ -5818,10 +6258,13 @@
       <c r="J146" s="3" t="n">
         <v>3.8</v>
       </c>
+      <c r="K146" s="6" t="n">
+        <v>1.196</v>
+      </c>
     </row>
     <row r="147" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A147" s="1" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="B147" s="5" t="n">
         <v>72.83</v>
@@ -5850,10 +6293,13 @@
       <c r="J147" s="3" t="n">
         <v>4</v>
       </c>
+      <c r="K147" s="6" t="n">
+        <v>2.8926</v>
+      </c>
     </row>
     <row r="148" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A148" s="1" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="B148" s="5" t="n">
         <v>35.54502</v>
@@ -5882,10 +6328,13 @@
       <c r="J148" s="3" t="n">
         <v>2.1</v>
       </c>
+      <c r="K148" s="6" t="n">
+        <v>0.7929</v>
+      </c>
     </row>
     <row r="149" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A149" s="1" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="B149" s="5" t="n">
         <v>31.046879</v>
@@ -5914,10 +6363,13 @@
       <c r="J149" s="3" t="n">
         <v>1.7</v>
       </c>
+      <c r="K149" s="6" t="n">
+        <v>0.5415</v>
+      </c>
     </row>
     <row r="150" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A150" s="1" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="B150" s="5" t="n">
         <v>38.324365</v>
@@ -5946,10 +6398,13 @@
       <c r="J150" s="3" t="n">
         <v>4.9</v>
       </c>
+      <c r="K150" s="6" t="n">
+        <v>1.6495</v>
+      </c>
     </row>
     <row r="151" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A151" s="1" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="B151" s="5" t="n">
         <v>32.780515</v>
@@ -5978,10 +6433,13 @@
       <c r="J151" s="3" t="n">
         <v>1.3</v>
       </c>
+      <c r="K151" s="6" t="n">
+        <v>1.3775</v>
+      </c>
     </row>
     <row r="152" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A152" s="1" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="B152" s="5" t="n">
         <v>56.732173</v>
@@ -6010,10 +6468,13 @@
       <c r="J152" s="3" t="n">
         <v>7.3</v>
       </c>
+      <c r="K152" s="6" t="n">
+        <v>4.3324</v>
+      </c>
     </row>
     <row r="153" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A153" s="1" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="B153" s="5" t="n">
         <v>33.863709</v>
@@ -6042,10 +6503,13 @@
       <c r="J153" s="3" t="n">
         <v>3.3</v>
       </c>
+      <c r="K153" s="6" t="n">
+        <v>1.8297</v>
+      </c>
     </row>
     <row r="154" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A154" s="1" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="B154" s="5" t="n">
         <v>40.346068</v>
@@ -6074,10 +6538,13 @@
       <c r="J154" s="3" t="n">
         <v>3.6</v>
       </c>
+      <c r="K154" s="6" t="n">
+        <v>0.6589</v>
+      </c>
     </row>
     <row r="155" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A155" s="1" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="B155" s="5" t="n">
         <v>48.716403</v>
@@ -6106,10 +6573,13 @@
       <c r="J155" s="3" t="n">
         <v>2.9</v>
       </c>
+      <c r="K155" s="6" t="n">
+        <v>2.4579</v>
+      </c>
     </row>
     <row r="156" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A156" s="1" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="B156" s="5" t="n">
         <v>39.901729</v>
@@ -6138,10 +6608,13 @@
       <c r="J156" s="3" t="n">
         <v>5.3</v>
       </c>
+      <c r="K156" s="6" t="n">
+        <v>3.5038</v>
+      </c>
     </row>
     <row r="157" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A157" s="1" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="B157" s="5" t="n">
         <v>37.00933</v>
@@ -6170,10 +6643,13 @@
       <c r="J157" s="3" t="n">
         <v>3.1</v>
       </c>
+      <c r="K157" s="6" t="n">
+        <v>2.0029</v>
+      </c>
     </row>
     <row r="158" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A158" s="1" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="B158" s="5" t="n">
         <v>39.31366</v>
@@ -6202,10 +6678,13 @@
       <c r="J158" s="3" t="n">
         <v>3.6</v>
       </c>
+      <c r="K158" s="6" t="n">
+        <v>2.3563</v>
+      </c>
     </row>
     <row r="159" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A159" s="1" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="B159" s="5" t="n">
         <v>37.088617</v>
@@ -6234,10 +6713,13 @@
       <c r="J159" s="3" t="n">
         <v>4.1</v>
       </c>
+      <c r="K159" s="6" t="n">
+        <v>2.4273</v>
+      </c>
     </row>
     <row r="160" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A160" s="1" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="B160" s="5" t="n">
         <v>36.110012</v>
@@ -6266,10 +6748,13 @@
       <c r="J160" s="3" t="n">
         <v>4.1</v>
       </c>
+      <c r="K160" s="6" t="n">
+        <v>2.8047</v>
+      </c>
     </row>
     <row r="161" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A161" s="1" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="B161" s="5" t="n">
         <v>47.191269</v>
@@ -6298,10 +6783,13 @@
       <c r="J161" s="3" t="n">
         <v>5.3</v>
       </c>
+      <c r="K161" s="6" t="n">
+        <v>3.6002</v>
+      </c>
     </row>
     <row r="162" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A162" s="1" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="B162" s="5" t="n">
         <v>39.942745</v>
@@ -6330,10 +6818,13 @@
       <c r="J162" s="3" t="n">
         <v>2.7</v>
       </c>
+      <c r="K162" s="6" t="n">
+        <v>1.5411</v>
+      </c>
     </row>
     <row r="163" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A163" s="1" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="B163" s="5" t="n">
         <v>43.050812</v>
@@ -6362,10 +6853,13 @@
       <c r="J163" s="3" t="n">
         <v>5.5</v>
       </c>
+      <c r="K163" s="6" t="n">
+        <v>3.9342</v>
+      </c>
     </row>
     <row r="164" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A164" s="1" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="B164" s="5" t="n">
         <v>43.989369</v>
@@ -6394,10 +6888,13 @@
       <c r="J164" s="3" t="n">
         <v>4.2</v>
       </c>
+      <c r="K164" s="6" t="n">
+        <v>1.4951</v>
+      </c>
     </row>
     <row r="165" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A165" s="1" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="B165" s="5" t="n">
         <v>35.04892</v>
@@ -6426,10 +6923,13 @@
       <c r="J165" s="3" t="n">
         <v>2.3</v>
       </c>
+      <c r="K165" s="6" t="n">
+        <v>1.843</v>
+      </c>
     </row>
     <row r="166" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A166" s="1" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="B166" s="5" t="n">
         <v>51.60112</v>
@@ -6458,10 +6958,13 @@
       <c r="J166" s="3" t="n">
         <v>7.2</v>
       </c>
+      <c r="K166" s="6" t="n">
+        <v>4.4958</v>
+      </c>
     </row>
     <row r="167" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A167" s="1" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="B167" s="5" t="n">
         <v>19.532798</v>
@@ -6490,10 +6993,13 @@
       <c r="J167" s="3" t="n">
         <v>0.8</v>
       </c>
+      <c r="K167" s="6" t="n">
+        <v>0.5555</v>
+      </c>
     </row>
     <row r="168" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A168" s="1" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="B168" s="5" t="n">
         <v>35.012154</v>
@@ -6522,10 +7028,13 @@
       <c r="J168" s="3" t="n">
         <v>4</v>
       </c>
+      <c r="K168" s="6" t="n">
+        <v>0.8446</v>
+      </c>
     </row>
     <row r="169" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A169" s="1" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="B169" s="5" t="n">
         <v>31.360723</v>
@@ -6554,10 +7063,13 @@
       <c r="J169" s="3" t="n">
         <v>2.6</v>
       </c>
+      <c r="K169" s="6" t="n">
+        <v>0.7251</v>
+      </c>
     </row>
     <row r="170" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A170" s="1" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="B170" s="5" t="n">
         <v>49.199691</v>
@@ -6586,10 +7098,13 @@
       <c r="J170" s="3" t="n">
         <v>6</v>
       </c>
+      <c r="K170" s="6" t="n">
+        <v>3.8869</v>
+      </c>
     </row>
     <row r="171" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A171" s="1" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="B171" s="5" t="n">
         <v>64.278703</v>
@@ -6618,10 +7133,13 @@
       <c r="J171" s="3" t="n">
         <v>7.3</v>
       </c>
+      <c r="K171" s="6" t="n">
+        <v>5.4792</v>
+      </c>
     </row>
     <row r="172" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A172" s="1" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="B172" s="5" t="n">
         <v>50.294922</v>
@@ -6650,10 +7168,13 @@
       <c r="J172" s="3" t="n">
         <v>4.8</v>
       </c>
+      <c r="K172" s="6" t="n">
+        <v>2.0511</v>
+      </c>
     </row>
     <row r="173" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A173" s="1" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="B173" s="5" t="n">
         <v>29.193112</v>
@@ -6682,10 +7203,13 @@
       <c r="J173" s="3" t="n">
         <v>1.5</v>
       </c>
+      <c r="K173" s="6" t="n">
+        <v>2.1732</v>
+      </c>
     </row>
     <row r="174" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A174" s="1" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="B174" s="5" t="n">
         <v>65.601235</v>
@@ -6714,10 +7238,13 @@
       <c r="J174" s="3" t="n">
         <v>9.3</v>
       </c>
+      <c r="K174" s="6" t="n">
+        <v>4.9534</v>
+      </c>
     </row>
     <row r="175" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A175" s="1" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="B175" s="5" t="n">
         <v>41.124411</v>
@@ -6746,10 +7273,13 @@
       <c r="J175" s="3" t="n">
         <v>2.2</v>
       </c>
+      <c r="K175" s="6" t="n">
+        <v>0.6432</v>
+      </c>
     </row>
     <row r="176" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A176" s="1" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="B176" s="5" t="n">
         <v>45.215247</v>
@@ -6778,10 +7308,13 @@
       <c r="J176" s="3" t="n">
         <v>4.9</v>
       </c>
+      <c r="K176" s="6" t="n">
+        <v>2.905</v>
+      </c>
     </row>
     <row r="177" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A177" s="1" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="B177" s="5" t="n">
         <v>58.583311</v>
@@ -6810,10 +7343,13 @@
       <c r="J177" s="3" t="n">
         <v>7.5</v>
       </c>
+      <c r="K177" s="6" t="n">
+        <v>4.3797</v>
+      </c>
     </row>
     <row r="178" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A178" s="1" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="B178" s="5" t="n">
         <v>46.58112</v>
@@ -6842,10 +7378,13 @@
       <c r="J178" s="3" t="n">
         <v>5.1</v>
       </c>
+      <c r="K178" s="6" t="n">
+        <v>3.5331</v>
+      </c>
     </row>
     <row r="179" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A179" s="1" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="B179" s="5" t="n">
         <v>49.747874</v>
@@ -6874,10 +7413,13 @@
       <c r="J179" s="3" t="n">
         <v>5.1</v>
       </c>
+      <c r="K179" s="6" t="n">
+        <v>3.6832</v>
+      </c>
     </row>
     <row r="180" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A180" s="1" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="B180" s="5" t="n">
         <v>18.69</v>
@@ -6906,10 +7448,13 @@
       <c r="J180" s="3" t="n">
         <v>1.3</v>
       </c>
+      <c r="K180" s="6" t="n">
+        <v>0.7905</v>
+      </c>
     </row>
     <row r="181" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A181" s="1" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="B181" s="5" t="n">
         <v>19.913169</v>
@@ -6938,10 +7483,13 @@
       <c r="J181" s="3" t="n">
         <v>1.5</v>
       </c>
+      <c r="K181" s="6" t="n">
+        <v>0.9664</v>
+      </c>
     </row>
     <row r="182" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A182" s="1" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="B182" s="5" t="n">
         <v>62.645063</v>
@@ -6970,10 +7518,13 @@
       <c r="J182" s="3" t="n">
         <v>6.9</v>
       </c>
+      <c r="K182" s="6" t="n">
+        <v>2.8864</v>
+      </c>
     </row>
     <row r="183" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A183" s="1" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="B183" s="5" t="n">
         <v>26.91321</v>
@@ -7002,10 +7553,13 @@
       <c r="J183" s="3" t="n">
         <v>2.3</v>
       </c>
+      <c r="K183" s="6" t="n">
+        <v>0.9667</v>
+      </c>
     </row>
     <row r="184" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A184" s="1" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="B184" s="5" t="n">
         <v>54.08259</v>
@@ -7034,10 +7588,13 @@
       <c r="J184" s="3" t="n">
         <v>4.6</v>
       </c>
+      <c r="K184" s="6" t="n">
+        <v>2.4912</v>
+      </c>
     </row>
     <row r="185" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A185" s="1" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="B185" s="5" t="n">
         <v>48.089369</v>
@@ -7066,10 +7623,13 @@
       <c r="J185" s="3" t="n">
         <v>6.3</v>
       </c>
+      <c r="K185" s="6" t="n">
+        <v>4.0953</v>
+      </c>
     </row>
     <row r="186" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A186" s="1" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="B186" s="5" t="n">
         <v>43.379</v>
@@ -7098,10 +7658,13 @@
       <c r="J186" s="3" t="n">
         <v>3.8</v>
       </c>
+      <c r="K186" s="6" t="n">
+        <v>2.185</v>
+      </c>
     </row>
     <row r="187" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A187" s="1" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="B187" s="5" t="n">
         <v>36.16772</v>
@@ -7130,10 +7693,13 @@
       <c r="J187" s="3" t="n">
         <v>3.2</v>
       </c>
+      <c r="K187" s="6" t="n">
+        <v>5.0185</v>
+      </c>
     </row>
     <row r="188" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A188" s="1" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="B188" s="5" t="n">
         <v>49.787933</v>
@@ -7162,10 +7728,13 @@
       <c r="J188" s="3" t="n">
         <v>5.7</v>
       </c>
+      <c r="K188" s="6" t="n">
+        <v>2.4668</v>
+      </c>
     </row>
     <row r="189" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A189" s="1" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="B189" s="5" t="n">
         <v>50.091269</v>
@@ -7194,10 +7763,13 @@
       <c r="J189" s="3" t="n">
         <v>6.7</v>
       </c>
+      <c r="K189" s="6" t="n">
+        <v>4.5506</v>
+      </c>
     </row>
     <row r="190" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A190" s="1" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="B190" s="5" t="n">
         <v>41.871532</v>
@@ -7226,10 +7798,13 @@
       <c r="J190" s="3" t="n">
         <v>4.2</v>
       </c>
+      <c r="K190" s="6" t="n">
+        <v>2.9592</v>
+      </c>
     </row>
     <row r="191" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A191" s="1" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="B191" s="5" t="n">
         <v>42.708992</v>
@@ -7258,10 +7833,13 @@
       <c r="J191" s="3" t="n">
         <v>3.4</v>
       </c>
+      <c r="K191" s="6" t="n">
+        <v>3.4251</v>
+      </c>
     </row>
     <row r="192" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A192" s="1" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="B192" s="5" t="n">
         <v>43.482459</v>
@@ -7290,10 +7868,13 @@
       <c r="J192" s="3" t="n">
         <v>4.3</v>
       </c>
+      <c r="K192" s="6" t="n">
+        <v>2.3084</v>
+      </c>
     </row>
     <row r="193" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A193" s="1" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="B193" s="5" t="n">
         <v>46.105132</v>
@@ -7322,10 +7903,13 @@
       <c r="J193" s="3" t="n">
         <v>4.2</v>
       </c>
+      <c r="K193" s="6" t="n">
+        <v>1.7056</v>
+      </c>
     </row>
     <row r="194" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A194" s="1" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="B194" s="5" t="n">
         <v>58.802066</v>
@@ -7354,10 +7938,13 @@
       <c r="J194" s="3" t="n">
         <v>5.1</v>
       </c>
+      <c r="K194" s="6" t="n">
+        <v>4.6824</v>
+      </c>
     </row>
     <row r="195" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A195" s="1" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="B195" s="5" t="n">
         <v>41.95258</v>
@@ -7386,10 +7973,13 @@
       <c r="J195" s="3" t="n">
         <v>4.7</v>
       </c>
+      <c r="K195" s="6" t="n">
+        <v>3.3212</v>
+      </c>
     </row>
     <row r="196" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A196" s="1" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="B196" s="5" t="n">
         <v>50.277656</v>
@@ -7418,10 +8008,13 @@
       <c r="J196" s="3" t="n">
         <v>6.6</v>
       </c>
+      <c r="K196" s="6" t="n">
+        <v>4.4081</v>
+      </c>
     </row>
     <row r="197" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A197" s="1" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="B197" s="5" t="n">
         <v>48.615732</v>
@@ -7450,10 +8043,13 @@
       <c r="J197" s="3" t="n">
         <v>3.8</v>
       </c>
+      <c r="K197" s="6" t="n">
+        <v>1.5383</v>
+      </c>
     </row>
     <row r="198" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A198" s="1" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="B198" s="5" t="n">
         <v>32.201165</v>
@@ -7482,10 +8078,13 @@
       <c r="J198" s="3" t="n">
         <v>3.1</v>
       </c>
+      <c r="K198" s="6" t="n">
+        <v>0.8959</v>
+      </c>
     </row>
     <row r="199" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A199" s="1" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="B199" s="5" t="n">
         <v>25.249359</v>
@@ -7514,10 +8113,13 @@
       <c r="J199" s="3" t="n">
         <v>1.5</v>
       </c>
+      <c r="K199" s="6" t="n">
+        <v>0.8384</v>
+      </c>
     </row>
     <row r="200" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A200" s="1" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="B200" s="5" t="n">
         <v>30.383985</v>
@@ -7546,10 +8148,13 @@
       <c r="J200" s="3" t="n">
         <v>3.3</v>
       </c>
+      <c r="K200" s="6" t="n">
+        <v>2.5371</v>
+      </c>
     </row>
     <row r="201" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A201" s="1" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="B201" s="5" t="n">
         <v>16.600327</v>
@@ -7578,10 +8183,13 @@
       <c r="J201" s="3" t="n">
         <v>2</v>
       </c>
+      <c r="K201" s="6" t="n">
+        <v>1.2065</v>
+      </c>
     </row>
     <row r="202" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A202" s="1" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="B202" s="5" t="n">
         <v>49.49824</v>
@@ -7610,10 +8218,13 @@
       <c r="J202" s="3" t="n">
         <v>3.6</v>
       </c>
+      <c r="K202" s="6" t="n">
+        <v>3.444</v>
+      </c>
     </row>
     <row r="203" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A203" s="1" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="B203" s="5" t="n">
         <v>44.288815</v>
@@ -7642,10 +8253,13 @@
       <c r="J203" s="3" t="n">
         <v>6.1</v>
       </c>
+      <c r="K203" s="6" t="n">
+        <v>3.1253</v>
+      </c>
     </row>
     <row r="204" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A204" s="1" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="B204" s="5" t="n">
         <v>64.208341</v>
@@ -7674,10 +8288,13 @@
       <c r="J204" s="3" t="n">
         <v>7.1</v>
       </c>
+      <c r="K204" s="6" t="n">
+        <v>4.3851</v>
+      </c>
     </row>
     <row r="205" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A205" s="1" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="B205" s="5" t="n">
         <v>45.073464</v>
@@ -7706,10 +8323,13 @@
       <c r="J205" s="3" t="n">
         <v>4.3</v>
       </c>
+      <c r="K205" s="6" t="n">
+        <v>2.7041</v>
+      </c>
     </row>
     <row r="206" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A206" s="1" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="B206" s="5" t="n">
         <v>35.643468</v>
@@ -7738,10 +8358,13 @@
       <c r="J206" s="3" t="n">
         <v>4.6</v>
       </c>
+      <c r="K206" s="6" t="n">
+        <v>1.2532</v>
+      </c>
     </row>
     <row r="207" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A207" s="1" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="B207" s="5" t="n">
         <v>48.995364</v>
@@ -7770,10 +8393,13 @@
       <c r="J207" s="3" t="n">
         <v>5.3</v>
       </c>
+      <c r="K207" s="6" t="n">
+        <v>2.7849</v>
+      </c>
     </row>
     <row r="208" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A208" s="1" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="B208" s="5" t="n">
         <v>62.830761</v>
@@ -7802,10 +8428,13 @@
       <c r="J208" s="3" t="n">
         <v>8.2</v>
       </c>
+      <c r="K208" s="6" t="n">
+        <v>2.3023</v>
+      </c>
     </row>
     <row r="209" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A209" s="1" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="B209" s="5" t="n">
         <v>49.774109</v>
@@ -7834,10 +8463,13 @@
       <c r="J209" s="3" t="n">
         <v>6.7</v>
       </c>
+      <c r="K209" s="6" t="n">
+        <v>3.5421</v>
+      </c>
     </row>
     <row r="210" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A210" s="1" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="B210" s="5" t="n">
         <v>56.580411</v>
@@ -7865,6 +8497,9 @@
       </c>
       <c r="J210" s="3" t="n">
         <v>6.1</v>
+      </c>
+      <c r="K210" s="6" t="n">
+        <v>3.7193</v>
       </c>
     </row>
   </sheetData>
@@ -7884,7 +8519,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:F36"/>
-  <sheetFormatPr defaultColWidth="11.23828125" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="11.2421875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="10.67"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="16.33"/>
@@ -7895,27 +8530,27 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="4" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="4" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="B2" s="2" t="n">
         <v>14.3</v>
@@ -7935,7 +8570,7 @@
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="4" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="B3" s="2" t="n">
         <v>24.2</v>
@@ -7955,7 +8590,7 @@
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="4" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="B4" s="2" t="n">
         <v>18.5</v>
@@ -7975,7 +8610,7 @@
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="4" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="B5" s="2" t="n">
         <v>18.4</v>
@@ -7995,7 +8630,7 @@
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="4" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="B6" s="2" t="n">
         <v>15.4</v>
@@ -8015,7 +8650,7 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="4" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="B7" s="2" t="n">
         <v>22.8</v>
@@ -8035,7 +8670,7 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="4" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="B8" s="2" t="n">
         <v>27</v>
@@ -8055,7 +8690,7 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="4" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="B9" s="2" t="n">
         <v>14.8</v>
@@ -8075,7 +8710,7 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="4" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="B10" s="2" t="n">
         <v>49.7</v>
@@ -8095,7 +8730,7 @@
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="4" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="B11" s="2" t="n">
         <v>9.1</v>
@@ -8115,7 +8750,7 @@
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="4" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="B12" s="2" t="n">
         <v>8.7</v>
@@ -8135,7 +8770,7 @@
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="4" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="B13" s="9" t="n">
         <v>30.6</v>
@@ -8155,7 +8790,7 @@
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="4" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="B14" s="2" t="n">
         <v>30.1</v>
@@ -8175,7 +8810,7 @@
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="4" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="B15" s="2" t="n">
         <v>15.6</v>
@@ -8195,7 +8830,7 @@
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="4" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="B16" s="2" t="n">
         <v>5.8</v>
@@ -8215,7 +8850,7 @@
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="4" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="B17" s="2" t="n">
         <v>51.5</v>
@@ -8235,7 +8870,7 @@
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="4" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="B18" s="2" t="n">
         <v>37.6</v>
@@ -8255,7 +8890,7 @@
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="4" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="B19" s="2" t="n">
         <v>36.8</v>
@@ -8275,7 +8910,7 @@
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="4" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="B20" s="2" t="n">
         <v>11.1</v>
@@ -8295,7 +8930,7 @@
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="4" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="B21" s="2" t="n">
         <v>34.8</v>
@@ -8315,7 +8950,7 @@
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="4" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="B22" s="2" t="n">
         <v>22</v>
@@ -8335,7 +8970,7 @@
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="4" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="B23" s="2" t="n">
         <v>17.4</v>
@@ -8355,7 +8990,7 @@
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="4" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="B24" s="2" t="n">
         <v>18.5</v>
@@ -8375,7 +9010,7 @@
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="4" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="B25" s="2" t="n">
         <v>19.4</v>
@@ -8395,7 +9030,7 @@
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="4" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="B26" s="2" t="n">
         <v>20.9</v>
@@ -8415,7 +9050,7 @@
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="4" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="B27" s="2" t="n">
         <v>28</v>
@@ -8435,7 +9070,7 @@
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="4" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="B28" s="2" t="n">
         <v>23.8</v>
@@ -8455,7 +9090,7 @@
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="4" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="B29" s="2" t="n">
         <v>30</v>
@@ -8475,7 +9110,7 @@
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="4" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="B30" s="2" t="n">
         <v>17.3</v>
@@ -8495,7 +9130,7 @@
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="4" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="B31" s="2" t="n">
         <v>10.6</v>
@@ -8515,7 +9150,7 @@
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="4" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="B32" s="2" t="n">
         <v>13.7</v>
@@ -8535,7 +9170,7 @@
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="4" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="B33" s="2" t="n">
         <v>19.1</v>
@@ -8555,7 +9190,7 @@
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="4" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="B34" s="2" t="n">
         <v>43.4</v>
@@ -8575,7 +9210,7 @@
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="4" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="B35" s="2" t="n">
         <v>18.6</v>
@@ -8595,7 +9230,7 @@
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="4" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="B36" s="2" t="n">
         <v>10.3</v>
@@ -8630,22 +9265,22 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:B5"/>
-  <sheetFormatPr defaultColWidth="11.23828125" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="11.2421875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="26" min="1" style="0" width="10.67"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="1" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="B2" s="1" t="n">
         <v>0</v>
@@ -8653,7 +9288,7 @@
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="1" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="B3" s="1" t="n">
         <v>0.33</v>
@@ -8661,7 +9296,7 @@
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="1" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="B4" s="1" t="n">
         <v>0.67</v>
@@ -8669,7 +9304,7 @@
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="1" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="B5" s="1" t="n">
         <v>1</v>
@@ -8692,28 +9327,28 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:C37"/>
-  <sheetFormatPr defaultColWidth="11.23828125" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="11.2421875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="26" min="1" style="0" width="10.67"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="1" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="C2" s="1" t="n">
         <v>0</v>
@@ -8721,10 +9356,10 @@
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="1" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="C3" s="1" t="n">
         <v>0.33</v>
@@ -8732,10 +9367,10 @@
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="1" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="C4" s="1" t="n">
         <v>1</v>
@@ -8743,10 +9378,10 @@
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="1" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="C5" s="1" t="n">
         <v>1</v>
@@ -8754,10 +9389,10 @@
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="1" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="C6" s="1" t="n">
         <v>0</v>
@@ -8765,10 +9400,10 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="1" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="C7" s="1" t="n">
         <v>0</v>
@@ -8776,10 +9411,10 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="1" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="C8" s="1" t="n">
         <v>0.67</v>
@@ -8787,10 +9422,10 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="1" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="C9" s="1" t="n">
         <v>0.33</v>
@@ -8798,10 +9433,10 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="1" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="C10" s="1" t="n">
         <v>0</v>
@@ -8809,10 +9444,10 @@
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="1" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="C11" s="1" t="n">
         <v>0</v>
@@ -8820,10 +9455,10 @@
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="1" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="C12" s="1" t="n">
         <v>0</v>
@@ -8831,10 +9466,10 @@
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="1" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="C13" s="1" t="n">
         <v>0.67</v>
@@ -8842,10 +9477,10 @@
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="1" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="C14" s="1" t="n">
         <v>0</v>
@@ -8853,10 +9488,10 @@
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="1" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="C15" s="1" t="n">
         <v>0.33</v>
@@ -8864,10 +9499,10 @@
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="1" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="C16" s="1" t="n">
         <v>0</v>
@@ -8875,10 +9510,10 @@
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="1" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="C17" s="1" t="n">
         <v>0</v>
@@ -8886,10 +9521,10 @@
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="1" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="C18" s="1" t="n">
         <v>0.33</v>
@@ -8897,10 +9532,10 @@
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="1" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="C19" s="1" t="n">
         <v>0</v>
@@ -8908,10 +9543,10 @@
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="1" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="C20" s="1" t="n">
         <v>0</v>
@@ -8919,10 +9554,10 @@
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="1" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="C21" s="1" t="n">
         <v>0</v>
@@ -8930,10 +9565,10 @@
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="1" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="C22" s="1" t="n">
         <v>0.33</v>
@@ -8941,10 +9576,10 @@
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="1" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="C23" s="1" t="n">
         <v>0.33</v>
@@ -8952,10 +9587,10 @@
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="1" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="C24" s="1" t="n">
         <v>0.67</v>
@@ -8963,10 +9598,10 @@
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="1" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="C25" s="1" t="n">
         <v>0</v>
@@ -8974,10 +9609,10 @@
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="1" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="C26" s="1" t="n">
         <v>0.33</v>
@@ -8985,10 +9620,10 @@
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="1" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="C27" s="1" t="n">
         <v>0.67</v>
@@ -8996,10 +9631,10 @@
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="1" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="C28" s="1" t="n">
         <v>1</v>
@@ -9007,10 +9642,10 @@
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="1" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="C29" s="1" t="n">
         <v>0.67</v>
@@ -9018,10 +9653,10 @@
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="1" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="C30" s="1" t="n">
         <v>0</v>
@@ -9029,10 +9664,10 @@
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="1" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="C31" s="1" t="n">
         <v>0.33</v>
@@ -9040,10 +9675,10 @@
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="1" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="C32" s="1" t="n">
         <v>0</v>
@@ -9051,10 +9686,10 @@
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="1" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="B33" s="1" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="C33" s="1" t="n">
         <v>0</v>
@@ -9062,10 +9697,10 @@
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="1" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="C34" s="1" t="n">
         <v>0</v>
@@ -9073,10 +9708,10 @@
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="1" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="B35" s="1" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="C35" s="1" t="n">
         <v>1</v>
@@ -9084,10 +9719,10 @@
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="1" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="C36" s="1" t="n">
         <v>0.33</v>
@@ -9095,10 +9730,10 @@
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="1" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="B37" s="1" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="C37" s="1" t="n">
         <v>1</v>
@@ -9121,235 +9756,235 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:BU36"/>
-  <sheetFormatPr defaultColWidth="11.23828125" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="11.2421875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="73" min="1" style="0" width="10.67"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
+        <v>220</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>269</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="N1" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="O1" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="P1" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="Q1" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="R1" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="S1" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="T1" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="U1" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="V1" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="W1" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="X1" s="1" t="s">
+        <v>270</v>
+      </c>
+      <c r="Y1" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="Z1" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="AA1" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="AB1" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="AC1" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="AD1" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="AE1" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="AF1" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="AG1" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="AH1" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="AI1" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="AJ1" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="AK1" s="1" t="s">
+        <v>119</v>
+      </c>
+      <c r="AL1" s="1" t="s">
+        <v>120</v>
+      </c>
+      <c r="AM1" s="1" t="s">
+        <v>121</v>
+      </c>
+      <c r="AN1" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="AO1" s="1" t="s">
+        <v>129</v>
+      </c>
+      <c r="AP1" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="AQ1" s="1" t="s">
+        <v>134</v>
+      </c>
+      <c r="AR1" s="1" t="s">
+        <v>135</v>
+      </c>
+      <c r="AS1" s="1" t="s">
+        <v>136</v>
+      </c>
+      <c r="AT1" s="1" t="s">
+        <v>137</v>
+      </c>
+      <c r="AU1" s="1" t="s">
+        <v>143</v>
+      </c>
+      <c r="AV1" s="1" t="s">
+        <v>144</v>
+      </c>
+      <c r="AW1" s="1" t="s">
+        <v>145</v>
+      </c>
+      <c r="AX1" s="1" t="s">
+        <v>150</v>
+      </c>
+      <c r="AY1" s="1" t="s">
+        <v>152</v>
+      </c>
+      <c r="AZ1" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="BA1" s="1" t="s">
+        <v>155</v>
+      </c>
+      <c r="BB1" s="1" t="s">
+        <v>271</v>
+      </c>
+      <c r="BC1" s="1" t="s">
+        <v>272</v>
+      </c>
+      <c r="BD1" s="1" t="s">
+        <v>165</v>
+      </c>
+      <c r="BE1" s="1" t="s">
+        <v>172</v>
+      </c>
+      <c r="BF1" s="1" t="s">
+        <v>175</v>
+      </c>
+      <c r="BG1" s="1" t="s">
+        <v>180</v>
+      </c>
+      <c r="BH1" s="1" t="s">
+        <v>181</v>
+      </c>
+      <c r="BI1" s="1" t="s">
+        <v>273</v>
+      </c>
+      <c r="BJ1" s="1" t="s">
+        <v>186</v>
+      </c>
+      <c r="BK1" s="1" t="s">
+        <v>187</v>
+      </c>
+      <c r="BL1" s="1" t="s">
+        <v>195</v>
+      </c>
+      <c r="BM1" s="1" t="s">
+        <v>198</v>
+      </c>
+      <c r="BN1" s="1" t="s">
+        <v>274</v>
+      </c>
+      <c r="BO1" s="1" t="s">
+        <v>202</v>
+      </c>
+      <c r="BP1" s="1" t="s">
+        <v>205</v>
+      </c>
+      <c r="BQ1" s="1" t="s">
+        <v>275</v>
+      </c>
+      <c r="BR1" s="1" t="s">
+        <v>213</v>
+      </c>
+      <c r="BS1" s="1" t="s">
+        <v>214</v>
+      </c>
+      <c r="BT1" s="1" t="s">
+        <v>218</v>
+      </c>
+      <c r="BU1" s="1" t="s">
         <v>219</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>268</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="K1" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="L1" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="M1" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="N1" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="O1" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="P1" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="Q1" s="1" t="s">
-        <v>98</v>
-      </c>
-      <c r="R1" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="S1" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="T1" s="1" t="s">
-        <v>60</v>
-      </c>
-      <c r="U1" s="1" t="s">
-        <v>61</v>
-      </c>
-      <c r="V1" s="1" t="s">
-        <v>62</v>
-      </c>
-      <c r="W1" s="1" t="s">
-        <v>68</v>
-      </c>
-      <c r="X1" s="1" t="s">
-        <v>269</v>
-      </c>
-      <c r="Y1" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="Z1" s="1" t="s">
-        <v>77</v>
-      </c>
-      <c r="AA1" s="1" t="s">
-        <v>82</v>
-      </c>
-      <c r="AB1" s="1" t="s">
-        <v>83</v>
-      </c>
-      <c r="AC1" s="1" t="s">
-        <v>85</v>
-      </c>
-      <c r="AD1" s="1" t="s">
-        <v>86</v>
-      </c>
-      <c r="AE1" s="1" t="s">
-        <v>91</v>
-      </c>
-      <c r="AF1" s="1" t="s">
-        <v>92</v>
-      </c>
-      <c r="AG1" s="1" t="s">
-        <v>93</v>
-      </c>
-      <c r="AH1" s="1" t="s">
-        <v>99</v>
-      </c>
-      <c r="AI1" s="1" t="s">
-        <v>103</v>
-      </c>
-      <c r="AJ1" s="1" t="s">
-        <v>112</v>
-      </c>
-      <c r="AK1" s="1" t="s">
-        <v>118</v>
-      </c>
-      <c r="AL1" s="1" t="s">
-        <v>119</v>
-      </c>
-      <c r="AM1" s="1" t="s">
-        <v>120</v>
-      </c>
-      <c r="AN1" s="1" t="s">
-        <v>122</v>
-      </c>
-      <c r="AO1" s="1" t="s">
-        <v>128</v>
-      </c>
-      <c r="AP1" s="1" t="s">
-        <v>131</v>
-      </c>
-      <c r="AQ1" s="1" t="s">
-        <v>133</v>
-      </c>
-      <c r="AR1" s="1" t="s">
-        <v>134</v>
-      </c>
-      <c r="AS1" s="1" t="s">
-        <v>135</v>
-      </c>
-      <c r="AT1" s="1" t="s">
-        <v>136</v>
-      </c>
-      <c r="AU1" s="1" t="s">
-        <v>142</v>
-      </c>
-      <c r="AV1" s="1" t="s">
-        <v>143</v>
-      </c>
-      <c r="AW1" s="1" t="s">
-        <v>144</v>
-      </c>
-      <c r="AX1" s="1" t="s">
-        <v>149</v>
-      </c>
-      <c r="AY1" s="1" t="s">
-        <v>151</v>
-      </c>
-      <c r="AZ1" s="1" t="s">
-        <v>152</v>
-      </c>
-      <c r="BA1" s="1" t="s">
-        <v>154</v>
-      </c>
-      <c r="BB1" s="1" t="s">
-        <v>270</v>
-      </c>
-      <c r="BC1" s="1" t="s">
-        <v>271</v>
-      </c>
-      <c r="BD1" s="1" t="s">
-        <v>164</v>
-      </c>
-      <c r="BE1" s="1" t="s">
-        <v>171</v>
-      </c>
-      <c r="BF1" s="1" t="s">
-        <v>174</v>
-      </c>
-      <c r="BG1" s="1" t="s">
-        <v>179</v>
-      </c>
-      <c r="BH1" s="1" t="s">
-        <v>180</v>
-      </c>
-      <c r="BI1" s="1" t="s">
-        <v>272</v>
-      </c>
-      <c r="BJ1" s="1" t="s">
-        <v>185</v>
-      </c>
-      <c r="BK1" s="1" t="s">
-        <v>186</v>
-      </c>
-      <c r="BL1" s="1" t="s">
-        <v>194</v>
-      </c>
-      <c r="BM1" s="1" t="s">
-        <v>197</v>
-      </c>
-      <c r="BN1" s="1" t="s">
-        <v>273</v>
-      </c>
-      <c r="BO1" s="1" t="s">
-        <v>201</v>
-      </c>
-      <c r="BP1" s="1" t="s">
-        <v>204</v>
-      </c>
-      <c r="BQ1" s="1" t="s">
-        <v>274</v>
-      </c>
-      <c r="BR1" s="1" t="s">
-        <v>212</v>
-      </c>
-      <c r="BS1" s="1" t="s">
-        <v>213</v>
-      </c>
-      <c r="BT1" s="1" t="s">
-        <v>217</v>
-      </c>
-      <c r="BU1" s="1" t="s">
-        <v>218</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="1" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="B2" s="1" t="n">
         <v>0</v>
@@ -9570,7 +10205,7 @@
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="1" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="B3" s="1" t="n">
         <v>0.45</v>
@@ -9791,7 +10426,7 @@
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="1" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="B4" s="1" t="n">
         <v>0</v>
@@ -10012,7 +10647,7 @@
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="1" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="B5" s="1" t="n">
         <v>0</v>
@@ -10233,7 +10868,7 @@
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="1" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="B6" s="1" t="n">
         <v>0</v>
@@ -10454,7 +11089,7 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="1" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="B7" s="1" t="n">
         <v>0</v>
@@ -10672,7 +11307,7 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="1" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="B8" s="1" t="n">
         <v>0</v>
@@ -10893,7 +11528,7 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="1" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="B9" s="1" t="n">
         <v>0</v>
@@ -11114,7 +11749,7 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="1" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="B10" s="1" t="n">
         <v>0</v>
@@ -11329,7 +11964,7 @@
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="1" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="B11" s="1" t="n">
         <v>0.25</v>
@@ -11550,7 +12185,7 @@
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="1" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="B12" s="1" t="n">
         <v>0</v>
@@ -11771,7 +12406,7 @@
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="1" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="B13" s="1" t="n">
         <v>0</v>
@@ -11992,7 +12627,7 @@
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="1" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="B14" s="1" t="n">
         <v>0</v>
@@ -12213,7 +12848,7 @@
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="1" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="B15" s="1" t="n">
         <v>0</v>
@@ -12434,7 +13069,7 @@
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="1" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="B16" s="1" t="n">
         <v>0</v>
@@ -12655,7 +13290,7 @@
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="1" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="B17" s="1" t="n">
         <v>0</v>
@@ -12876,7 +13511,7 @@
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="1" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="B18" s="1" t="n">
         <v>0</v>
@@ -13097,7 +13732,7 @@
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="1" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="B19" s="1" t="n">
         <v>0</v>
@@ -13318,7 +13953,7 @@
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="1" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="B20" s="1" t="n">
         <v>0</v>
@@ -13539,7 +14174,7 @@
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="1" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="B21" s="1" t="n">
         <v>0</v>
@@ -13760,7 +14395,7 @@
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="1" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="B22" s="1" t="n">
         <v>0</v>
@@ -13981,7 +14616,7 @@
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="1" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="B23" s="1" t="n">
         <v>0</v>
@@ -14202,7 +14837,7 @@
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="1" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="B24" s="1" t="n">
         <v>0</v>
@@ -14423,7 +15058,7 @@
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="1" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="B25" s="1" t="n">
         <v>0</v>
@@ -14644,7 +15279,7 @@
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="1" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="B26" s="1" t="n">
         <v>0</v>
@@ -14865,7 +15500,7 @@
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="1" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="B27" s="1" t="n">
         <v>0</v>
@@ -15086,7 +15721,7 @@
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="1" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="B28" s="1" t="n">
         <v>0</v>
@@ -15304,7 +15939,7 @@
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="1" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="B29" s="1" t="n">
         <v>0</v>
@@ -15525,7 +16160,7 @@
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="1" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="B30" s="1" t="n">
         <v>0</v>
@@ -15746,7 +16381,7 @@
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="1" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="B31" s="1" t="n">
         <v>0</v>
@@ -15967,7 +16602,7 @@
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="1" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="B32" s="1" t="n">
         <v>0</v>
@@ -16188,7 +16823,7 @@
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="1" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="B33" s="1" t="n">
         <v>0</v>
@@ -16409,7 +17044,7 @@
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="1" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="B34" s="1" t="n">
         <v>0</v>
@@ -16630,7 +17265,7 @@
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="1" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="B35" s="1" t="n">
         <v>0.11</v>
@@ -16848,7 +17483,7 @@
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="1" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="B36" s="1" t="n">
         <v>0</v>
@@ -17084,31 +17719,31 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:E25"/>
-  <sheetFormatPr defaultColWidth="11.23828125" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="11.2421875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="26" min="1" style="0" width="10.67"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="1" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="B2" s="10" t="n">
         <v>5968</v>
@@ -17125,7 +17760,7 @@
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="1" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="B3" s="2" t="n">
         <v>747</v>
@@ -17142,7 +17777,7 @@
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="1" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="B4" s="2" t="n">
         <v>889</v>
@@ -17159,7 +17794,7 @@
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="1" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="B5" s="10" t="n">
         <v>1135</v>
@@ -17176,7 +17811,7 @@
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="1" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="B6" s="10" t="n">
         <v>1025</v>
@@ -17193,7 +17828,7 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="1" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="B7" s="2" t="n">
         <v>765</v>
@@ -17210,7 +17845,7 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="1" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="B8" s="10" t="n">
         <v>1230</v>
@@ -17227,7 +17862,7 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="1" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="B9" s="10" t="n">
         <v>1693</v>
@@ -17244,7 +17879,7 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="1" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="B10" s="2" t="n">
         <v>50</v>
@@ -17261,7 +17896,7 @@
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="1" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="B11" s="10" t="n">
         <v>2824</v>
@@ -17278,7 +17913,7 @@
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="1" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="B12" s="2" t="n">
         <v>286</v>
@@ -17295,7 +17930,7 @@
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="1" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="B13" s="2" t="n">
         <v>117</v>
@@ -17312,7 +17947,7 @@
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="1" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="B14" s="10" t="n">
         <v>1606</v>
@@ -17329,7 +17964,7 @@
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="1" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="B15" s="2" t="n">
         <v>720</v>
@@ -17346,7 +17981,7 @@
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="1" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="B16" s="2" t="n">
         <v>190</v>
@@ -17363,7 +17998,7 @@
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="1" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="B17" s="10" t="n">
         <v>8127</v>
@@ -17380,7 +18015,7 @@
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="1" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="B18" s="10" t="n">
         <v>2949</v>
@@ -17397,7 +18032,7 @@
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="1" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="B19" s="2" t="n">
         <v>881</v>
@@ -17414,7 +18049,7 @@
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="1" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="B20" s="10" t="n">
         <v>1958</v>
@@ -17431,7 +18066,7 @@
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="1" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="B21" s="2" t="n">
         <v>535</v>
@@ -17448,7 +18083,7 @@
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="1" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="B22" s="10" t="n">
         <v>2119</v>
@@ -17465,7 +18100,7 @@
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="1" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="B23" s="10" t="n">
         <v>1462</v>
@@ -17482,7 +18117,7 @@
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="1" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="B24" s="10" t="n">
         <v>1469</v>
@@ -17499,7 +18134,7 @@
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="1" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="B25" s="10" t="n">
         <v>38745</v>
@@ -17531,25 +18166,25 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:C11"/>
-  <sheetFormatPr defaultColWidth="11.23828125" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="11.2421875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="26" min="1" style="0" width="10.67"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="4" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="B1" s="4" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="C1" s="4" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="4" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="B2" s="4"/>
       <c r="C2" s="4" t="n">
@@ -17558,7 +18193,7 @@
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="4" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="B3" s="4"/>
       <c r="C3" s="4" t="n">
@@ -17567,7 +18202,7 @@
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="4" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="B4" s="4"/>
       <c r="C4" s="4" t="n">
@@ -17576,7 +18211,7 @@
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="4" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="B5" s="4"/>
       <c r="C5" s="4" t="n">
@@ -17585,10 +18220,10 @@
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="4" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="C6" s="4" t="n">
         <v>50</v>
@@ -17596,7 +18231,7 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="4" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="B7" s="4"/>
       <c r="C7" s="4" t="n">
@@ -17605,10 +18240,10 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="4" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="C8" s="4" t="n">
         <v>0.05</v>
@@ -17616,10 +18251,10 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="4" t="s">
+        <v>317</v>
+      </c>
+      <c r="B9" s="4" t="s">
         <v>316</v>
-      </c>
-      <c r="B9" s="4" t="s">
-        <v>315</v>
       </c>
       <c r="C9" s="4" t="n">
         <v>20</v>
@@ -17627,10 +18262,10 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="4" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="C10" s="4" t="n">
         <v>75</v>
@@ -17638,10 +18273,10 @@
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="4" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="C11" s="4" t="n">
         <v>0.25</v>

--- a/Data point Supporting files/Germany 2021/Indicators.xlsx
+++ b/Data point Supporting files/Germany 2021/Indicators.xlsx
@@ -5,7 +5,7 @@
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="6"/>
   </bookViews>
   <sheets>
     <sheet name="Indicators by country" sheetId="1" state="visible" r:id="rId2"/>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="497" uniqueCount="321">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="498" uniqueCount="322">
   <si>
     <t xml:space="preserve">Country</t>
   </si>
@@ -989,6 +989,9 @@
   </si>
   <si>
     <t xml:space="preserve">-</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Disaster coping capacity</t>
   </si>
 </sst>
 </file>
@@ -1076,7 +1079,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="10">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -1109,10 +1112,6 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
     <xf numFmtId="168" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -1139,7 +1138,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:K210"/>
-  <sheetFormatPr defaultColWidth="11.2421875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="11.2578125" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="10.67"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="10.44"/>
@@ -5767,7 +5766,9 @@
       <c r="I132" s="1" t="n">
         <v>0.656</v>
       </c>
-      <c r="J132" s="8"/>
+      <c r="J132" s="3" t="n">
+        <v>2</v>
+      </c>
       <c r="K132" s="6" t="n">
         <v>0.5233</v>
       </c>
@@ -8519,7 +8520,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:F36"/>
-  <sheetFormatPr defaultColWidth="11.2421875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="11.2578125" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="10.67"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="16.33"/>
@@ -8772,7 +8773,7 @@
       <c r="A13" s="4" t="s">
         <v>237</v>
       </c>
-      <c r="B13" s="9" t="n">
+      <c r="B13" s="8" t="n">
         <v>30.6</v>
       </c>
       <c r="C13" s="1" t="n">
@@ -9265,7 +9266,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:B5"/>
-  <sheetFormatPr defaultColWidth="11.2421875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="11.2578125" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="26" min="1" style="0" width="10.67"/>
   </cols>
@@ -9327,7 +9328,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:C37"/>
-  <sheetFormatPr defaultColWidth="11.2421875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="11.2578125" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="26" min="1" style="0" width="10.67"/>
   </cols>
@@ -9756,7 +9757,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:BU36"/>
-  <sheetFormatPr defaultColWidth="11.2421875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="11.2578125" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="73" min="1" style="0" width="10.67"/>
   </cols>
@@ -17719,7 +17720,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:E25"/>
-  <sheetFormatPr defaultColWidth="11.2421875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="11.2578125" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="26" min="1" style="0" width="10.67"/>
   </cols>
@@ -17745,16 +17746,16 @@
       <c r="A2" s="1" t="s">
         <v>281</v>
       </c>
-      <c r="B2" s="10" t="n">
+      <c r="B2" s="9" t="n">
         <v>5968</v>
       </c>
-      <c r="C2" s="10" t="n">
+      <c r="C2" s="9" t="n">
         <v>729157</v>
       </c>
-      <c r="D2" s="10" t="n">
+      <c r="D2" s="9" t="n">
         <v>180279441</v>
       </c>
-      <c r="E2" s="10" t="n">
+      <c r="E2" s="9" t="n">
         <v>37682105</v>
       </c>
     </row>
@@ -17765,13 +17766,13 @@
       <c r="B3" s="2" t="n">
         <v>747</v>
       </c>
-      <c r="C3" s="10" t="n">
+      <c r="C3" s="9" t="n">
         <v>92576</v>
       </c>
-      <c r="D3" s="10" t="n">
+      <c r="D3" s="9" t="n">
         <v>43107620</v>
       </c>
-      <c r="E3" s="10" t="n">
+      <c r="E3" s="9" t="n">
         <v>20164228</v>
       </c>
     </row>
@@ -17782,13 +17783,13 @@
       <c r="B4" s="2" t="n">
         <v>889</v>
       </c>
-      <c r="C4" s="10" t="n">
+      <c r="C4" s="9" t="n">
         <v>87135</v>
       </c>
-      <c r="D4" s="10" t="n">
+      <c r="D4" s="9" t="n">
         <v>18094361</v>
       </c>
-      <c r="E4" s="10" t="n">
+      <c r="E4" s="9" t="n">
         <v>5739135</v>
       </c>
     </row>
@@ -17796,16 +17797,16 @@
       <c r="A5" s="1" t="s">
         <v>284</v>
       </c>
-      <c r="B5" s="10" t="n">
+      <c r="B5" s="9" t="n">
         <v>1135</v>
       </c>
-      <c r="C5" s="10" t="n">
+      <c r="C5" s="9" t="n">
         <v>93665</v>
       </c>
-      <c r="D5" s="10" t="n">
+      <c r="D5" s="9" t="n">
         <v>27354753</v>
       </c>
-      <c r="E5" s="10" t="n">
+      <c r="E5" s="9" t="n">
         <v>8870958</v>
       </c>
     </row>
@@ -17813,16 +17814,16 @@
       <c r="A6" s="1" t="s">
         <v>285</v>
       </c>
-      <c r="B6" s="10" t="n">
+      <c r="B6" s="9" t="n">
         <v>1025</v>
       </c>
-      <c r="C6" s="10" t="n">
+      <c r="C6" s="9" t="n">
         <v>100339</v>
       </c>
-      <c r="D6" s="10" t="n">
+      <c r="D6" s="9" t="n">
         <v>19283449</v>
       </c>
-      <c r="E6" s="10" t="n">
+      <c r="E6" s="9" t="n">
         <v>6354803</v>
       </c>
     </row>
@@ -17833,13 +17834,13 @@
       <c r="B7" s="2" t="n">
         <v>765</v>
       </c>
-      <c r="C7" s="10" t="n">
+      <c r="C7" s="9" t="n">
         <v>129502</v>
       </c>
-      <c r="D7" s="10" t="n">
+      <c r="D7" s="9" t="n">
         <v>43786506</v>
       </c>
-      <c r="E7" s="10" t="n">
+      <c r="E7" s="9" t="n">
         <v>10562891</v>
       </c>
     </row>
@@ -17847,16 +17848,16 @@
       <c r="A8" s="1" t="s">
         <v>287</v>
       </c>
-      <c r="B8" s="10" t="n">
+      <c r="B8" s="9" t="n">
         <v>1230</v>
       </c>
-      <c r="C8" s="10" t="n">
+      <c r="C8" s="9" t="n">
         <v>93241</v>
       </c>
-      <c r="D8" s="10" t="n">
+      <c r="D8" s="9" t="n">
         <v>12843863</v>
       </c>
-      <c r="E8" s="10" t="n">
+      <c r="E8" s="9" t="n">
         <v>4937419</v>
       </c>
     </row>
@@ -17864,16 +17865,16 @@
       <c r="A9" s="1" t="s">
         <v>288</v>
       </c>
-      <c r="B9" s="10" t="n">
+      <c r="B9" s="9" t="n">
         <v>1693</v>
       </c>
-      <c r="C9" s="10" t="n">
+      <c r="C9" s="9" t="n">
         <v>490018</v>
       </c>
-      <c r="D9" s="10" t="n">
+      <c r="D9" s="9" t="n">
         <v>259704167</v>
       </c>
-      <c r="E9" s="10" t="n">
+      <c r="E9" s="9" t="n">
         <v>70359228</v>
       </c>
     </row>
@@ -17884,13 +17885,13 @@
       <c r="B10" s="2" t="n">
         <v>50</v>
       </c>
-      <c r="C10" s="10" t="n">
+      <c r="C10" s="9" t="n">
         <v>19150</v>
       </c>
-      <c r="D10" s="10" t="n">
+      <c r="D10" s="9" t="n">
         <v>70971297</v>
       </c>
-      <c r="E10" s="10" t="n">
+      <c r="E10" s="9" t="n">
         <v>36521537</v>
       </c>
     </row>
@@ -17898,16 +17899,16 @@
       <c r="A11" s="1" t="s">
         <v>290</v>
       </c>
-      <c r="B11" s="10" t="n">
+      <c r="B11" s="9" t="n">
         <v>2824</v>
       </c>
-      <c r="C11" s="10" t="n">
+      <c r="C11" s="9" t="n">
         <v>332975</v>
       </c>
-      <c r="D11" s="10" t="n">
+      <c r="D11" s="9" t="n">
         <v>75096525</v>
       </c>
-      <c r="E11" s="10" t="n">
+      <c r="E11" s="9" t="n">
         <v>23969099</v>
       </c>
     </row>
@@ -17918,13 +17919,13 @@
       <c r="B12" s="2" t="n">
         <v>286</v>
       </c>
-      <c r="C12" s="10" t="n">
+      <c r="C12" s="9" t="n">
         <v>72723</v>
       </c>
-      <c r="D12" s="10" t="n">
+      <c r="D12" s="9" t="n">
         <v>19378255</v>
       </c>
-      <c r="E12" s="10" t="n">
+      <c r="E12" s="9" t="n">
         <v>6330572</v>
       </c>
     </row>
@@ -17935,13 +17936,13 @@
       <c r="B13" s="2" t="n">
         <v>117</v>
       </c>
-      <c r="C13" s="10" t="n">
+      <c r="C13" s="9" t="n">
         <v>12765</v>
       </c>
-      <c r="D13" s="10" t="n">
+      <c r="D13" s="9" t="n">
         <v>2618046</v>
       </c>
-      <c r="E13" s="10" t="n">
+      <c r="E13" s="9" t="n">
         <v>799236</v>
       </c>
     </row>
@@ -17949,16 +17950,16 @@
       <c r="A14" s="1" t="s">
         <v>293</v>
       </c>
-      <c r="B14" s="10" t="n">
+      <c r="B14" s="9" t="n">
         <v>1606</v>
       </c>
-      <c r="C14" s="10" t="n">
+      <c r="C14" s="9" t="n">
         <v>201861</v>
       </c>
-      <c r="D14" s="10" t="n">
+      <c r="D14" s="9" t="n">
         <v>50622230</v>
       </c>
-      <c r="E14" s="10" t="n">
+      <c r="E14" s="9" t="n">
         <v>17308377</v>
       </c>
     </row>
@@ -17969,13 +17970,13 @@
       <c r="B15" s="2" t="n">
         <v>720</v>
       </c>
-      <c r="C15" s="10" t="n">
+      <c r="C15" s="9" t="n">
         <v>180490</v>
       </c>
-      <c r="D15" s="10" t="n">
+      <c r="D15" s="9" t="n">
         <v>69516462</v>
       </c>
-      <c r="E15" s="10" t="n">
+      <c r="E15" s="9" t="n">
         <v>15052955</v>
       </c>
     </row>
@@ -17986,13 +17987,13 @@
       <c r="B16" s="2" t="n">
         <v>190</v>
       </c>
-      <c r="C16" s="10" t="n">
+      <c r="C16" s="9" t="n">
         <v>56503</v>
       </c>
-      <c r="D16" s="10" t="n">
+      <c r="D16" s="9" t="n">
         <v>49143912</v>
       </c>
-      <c r="E16" s="10" t="n">
+      <c r="E16" s="9" t="n">
         <v>6913696</v>
       </c>
     </row>
@@ -18000,16 +18001,16 @@
       <c r="A17" s="1" t="s">
         <v>296</v>
       </c>
-      <c r="B17" s="10" t="n">
+      <c r="B17" s="9" t="n">
         <v>8127</v>
       </c>
-      <c r="C17" s="10" t="n">
+      <c r="C17" s="9" t="n">
         <v>686805</v>
       </c>
-      <c r="D17" s="10" t="n">
+      <c r="D17" s="9" t="n">
         <v>127623698</v>
       </c>
-      <c r="E17" s="10" t="n">
+      <c r="E17" s="9" t="n">
         <v>49197043</v>
       </c>
     </row>
@@ -18017,16 +18018,16 @@
       <c r="A18" s="1" t="s">
         <v>297</v>
       </c>
-      <c r="B18" s="10" t="n">
+      <c r="B18" s="9" t="n">
         <v>2949</v>
       </c>
-      <c r="C18" s="10" t="n">
+      <c r="C18" s="9" t="n">
         <v>657265</v>
       </c>
-      <c r="D18" s="10" t="n">
+      <c r="D18" s="9" t="n">
         <v>178771869</v>
       </c>
-      <c r="E18" s="10" t="n">
+      <c r="E18" s="9" t="n">
         <v>61664006</v>
       </c>
     </row>
@@ -18037,13 +18038,13 @@
       <c r="B19" s="2" t="n">
         <v>881</v>
       </c>
-      <c r="C19" s="10" t="n">
+      <c r="C19" s="9" t="n">
         <v>145519</v>
       </c>
-      <c r="D19" s="10" t="n">
+      <c r="D19" s="9" t="n">
         <v>37024478</v>
       </c>
-      <c r="E19" s="10" t="n">
+      <c r="E19" s="9" t="n">
         <v>12653885</v>
       </c>
     </row>
@@ -18051,16 +18052,16 @@
       <c r="A20" s="1" t="s">
         <v>299</v>
       </c>
-      <c r="B20" s="10" t="n">
+      <c r="B20" s="9" t="n">
         <v>1958</v>
       </c>
-      <c r="C20" s="10" t="n">
+      <c r="C20" s="9" t="n">
         <v>273018</v>
       </c>
-      <c r="D20" s="10" t="n">
+      <c r="D20" s="9" t="n">
         <v>64145550</v>
       </c>
-      <c r="E20" s="10" t="n">
+      <c r="E20" s="9" t="n">
         <v>22341674</v>
       </c>
     </row>
@@ -18071,13 +18072,13 @@
       <c r="B21" s="2" t="n">
         <v>535</v>
       </c>
-      <c r="C21" s="10" t="n">
+      <c r="C21" s="9" t="n">
         <v>88474</v>
       </c>
-      <c r="D21" s="10" t="n">
+      <c r="D21" s="9" t="n">
         <v>26749122</v>
       </c>
-      <c r="E21" s="10" t="n">
+      <c r="E21" s="9" t="n">
         <v>8320270</v>
       </c>
     </row>
@@ -18085,16 +18086,16 @@
       <c r="A22" s="1" t="s">
         <v>301</v>
       </c>
-      <c r="B22" s="10" t="n">
+      <c r="B22" s="9" t="n">
         <v>2119</v>
       </c>
-      <c r="C22" s="10" t="n">
+      <c r="C22" s="9" t="n">
         <v>460020</v>
       </c>
-      <c r="D22" s="10" t="n">
+      <c r="D22" s="9" t="n">
         <v>126526058</v>
       </c>
-      <c r="E22" s="10" t="n">
+      <c r="E22" s="9" t="n">
         <v>43892222</v>
       </c>
     </row>
@@ -18102,16 +18103,16 @@
       <c r="A23" s="1" t="s">
         <v>302</v>
       </c>
-      <c r="B23" s="10" t="n">
+      <c r="B23" s="9" t="n">
         <v>1462</v>
       </c>
-      <c r="C23" s="10" t="n">
+      <c r="C23" s="9" t="n">
         <v>248704</v>
       </c>
-      <c r="D23" s="10" t="n">
+      <c r="D23" s="9" t="n">
         <v>65367631</v>
       </c>
-      <c r="E23" s="10" t="n">
+      <c r="E23" s="9" t="n">
         <v>26690958</v>
       </c>
     </row>
@@ -18119,16 +18120,16 @@
       <c r="A24" s="1" t="s">
         <v>303</v>
       </c>
-      <c r="B24" s="10" t="n">
+      <c r="B24" s="9" t="n">
         <v>1469</v>
       </c>
-      <c r="C24" s="10" t="n">
+      <c r="C24" s="9" t="n">
         <v>960800</v>
       </c>
-      <c r="D24" s="10" t="n">
+      <c r="D24" s="9" t="n">
         <v>549855814</v>
       </c>
-      <c r="E24" s="10" t="n">
+      <c r="E24" s="9" t="n">
         <v>117457923</v>
       </c>
     </row>
@@ -18136,16 +18137,16 @@
       <c r="A25" s="1" t="s">
         <v>304</v>
       </c>
-      <c r="B25" s="10" t="n">
+      <c r="B25" s="9" t="n">
         <v>38745</v>
       </c>
-      <c r="C25" s="10" t="n">
+      <c r="C25" s="9" t="n">
         <v>6212705</v>
       </c>
-      <c r="D25" s="10" t="n">
+      <c r="D25" s="9" t="n">
         <v>2117865107</v>
       </c>
-      <c r="E25" s="10" t="n">
+      <c r="E25" s="9" t="n">
         <v>613784220</v>
       </c>
     </row>
@@ -18165,8 +18166,8 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:C11"/>
-  <sheetFormatPr defaultColWidth="11.2421875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <dimension ref="A1:C12"/>
+  <sheetFormatPr defaultColWidth="11.2578125" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="26" min="1" style="0" width="10.67"/>
   </cols>
@@ -18280,6 +18281,14 @@
       </c>
       <c r="C11" s="4" t="n">
         <v>0.25</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A12" s="0" t="s">
+        <v>321</v>
+      </c>
+      <c r="C12" s="0" t="n">
+        <v>3</v>
       </c>
     </row>
   </sheetData>
